--- a/research/traditional_assets/database/data/cayman_islands/cayman_islands_education.xlsx
+++ b/research/traditional_assets/database/data/cayman_islands/cayman_islands_education.xlsx
@@ -1127,43 +1127,43 @@
         <v>0.805520702634881</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>44.39889304614</v>
       </c>
       <c r="G2">
         <v>19.236641221374</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.737404580152672</v>
       </c>
       <c r="I2">
         <v>0.260869565217391</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>35.7</v>
       </c>
       <c r="L2">
-        <v>51.5159791112116</v>
+        <v>50.9933352437214</v>
       </c>
       <c r="M2">
         <v>30.8</v>
       </c>
       <c r="N2">
-        <v>34.0159791112116</v>
+        <v>33.9763352437214</v>
       </c>
       <c r="O2">
         <v>12.6</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>0.483</v>
       </c>
       <c r="Q2">
         <v>0.08839369245413869</v>
       </c>
       <c r="R2">
-        <v>0.0843667489769559</v>
+        <v>0.0844117489769559</v>
       </c>
       <c r="S2">
         <v>0.0612366166625341</v>
@@ -1185,13 +1185,13 @@
         <v>0.0979785427335286</v>
       </c>
       <c r="X2">
-        <v>0.0843667489769559</v>
+        <v>0.0847563120979353</v>
       </c>
       <c r="Y2">
         <v>1.01705691774699</v>
       </c>
       <c r="Z2">
-        <v>0.751737721812992</v>
+        <v>0.7593310321343359</v>
       </c>
       <c r="AA2">
         <v>12.6</v>
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08436674897695591</v>
+        <v>0.08441174897695593</v>
       </c>
       <c r="C2">
-        <v>51.51597911121158</v>
+        <v>50.99333524372144</v>
       </c>
       <c r="D2">
-        <v>34.01597911121158</v>
+        <v>33.97633524372144</v>
       </c>
       <c r="E2">
-        <v>-12.6</v>
+        <v>-12.117</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.483</v>
       </c>
       <c r="G2">
         <v>17.5</v>
@@ -1445,28 +1445,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0242949</v>
       </c>
       <c r="N2">
-        <v>1.078666666666667</v>
+        <v>1.054371766666667</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>1.078666666666667</v>
+        <v>1.054371766666667</v>
       </c>
       <c r="Q2">
-        <v>1.091666666666667</v>
+        <v>1.067371766666667</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08436674897695591</v>
+        <v>0.08475631209793527</v>
       </c>
       <c r="T2">
-        <v>0.7517377218129921</v>
+        <v>0.7593310321343355</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>44.39889304614001</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08441174897695593</v>
+        <v>0.0844567489769559</v>
       </c>
       <c r="C3">
-        <v>50.99333524372144</v>
+        <v>50.47078367442423</v>
       </c>
       <c r="D3">
-        <v>33.97633524372144</v>
+        <v>33.93678367442423</v>
       </c>
       <c r="E3">
-        <v>-12.117</v>
+        <v>-11.634</v>
       </c>
       <c r="F3">
-        <v>0.483</v>
+        <v>0.9660000000000001</v>
       </c>
       <c r="G3">
         <v>17.5</v>
@@ -1527,28 +1527,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M3">
-        <v>0.0242949</v>
+        <v>0.0485898</v>
       </c>
       <c r="N3">
-        <v>1.054371766666667</v>
+        <v>1.030076866666667</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>1.054371766666667</v>
+        <v>1.030076866666667</v>
       </c>
       <c r="Q3">
-        <v>1.067371766666667</v>
+        <v>1.043076866666667</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08475631209793527</v>
+        <v>0.0851538254866897</v>
       </c>
       <c r="T3">
-        <v>0.7593310321343355</v>
+        <v>0.7670793079724409</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>44.39889304614001</v>
+        <v>22.19944652307</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0844567489769559</v>
+        <v>0.08450174897695591</v>
       </c>
       <c r="C4">
-        <v>50.47078367442423</v>
+        <v>49.94832408136402</v>
       </c>
       <c r="D4">
-        <v>33.93678367442423</v>
+        <v>33.89732408136402</v>
       </c>
       <c r="E4">
-        <v>-11.634</v>
+        <v>-11.151</v>
       </c>
       <c r="F4">
-        <v>0.9660000000000001</v>
+        <v>1.449</v>
       </c>
       <c r="G4">
         <v>17.5</v>
@@ -1609,28 +1609,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M4">
-        <v>0.0485898</v>
+        <v>0.0728847</v>
       </c>
       <c r="N4">
-        <v>1.030076866666667</v>
+        <v>1.005781966666667</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>1.030076866666667</v>
+        <v>1.005781966666667</v>
       </c>
       <c r="Q4">
-        <v>1.043076866666667</v>
+        <v>1.018781966666667</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.0851538254866897</v>
+        <v>0.0855595350277896</v>
       </c>
       <c r="T4">
-        <v>0.7670793079724409</v>
+        <v>0.7749873420752496</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>22.19944652307</v>
+        <v>14.79963101538</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08450174897695591</v>
+        <v>0.0846067489769559</v>
       </c>
       <c r="C5">
-        <v>49.94832408136402</v>
+        <v>49.37360758559014</v>
       </c>
       <c r="D5">
-        <v>33.89732408136402</v>
+        <v>33.80560758559014</v>
       </c>
       <c r="E5">
-        <v>-11.151</v>
+        <v>-10.668</v>
       </c>
       <c r="F5">
-        <v>1.449</v>
+        <v>1.932</v>
       </c>
       <c r="G5">
         <v>17.5</v>
@@ -1691,45 +1691,45 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M5">
-        <v>0.0728847</v>
+        <v>0.1000776</v>
       </c>
       <c r="N5">
-        <v>1.005781966666667</v>
+        <v>0.9785890666666669</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>1.005781966666667</v>
+        <v>0.9785890666666669</v>
       </c>
       <c r="Q5">
-        <v>1.018781966666667</v>
+        <v>0.9915890666666669</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.0855595350277896</v>
+        <v>0.08597369685099573</v>
       </c>
       <c r="T5">
-        <v>0.7749873420752496</v>
+        <v>0.7830601268885335</v>
       </c>
       <c r="U5">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V5">
         <v>0</v>
       </c>
       <c r="W5">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y5">
-        <v>14.79963101538</v>
+        <v>10.77830270376854</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0846067489769559</v>
+        <v>0.08475174897695589</v>
       </c>
       <c r="C6">
-        <v>49.37360758559014</v>
+        <v>48.76476437626955</v>
       </c>
       <c r="D6">
-        <v>33.80560758559014</v>
+        <v>33.67976437626955</v>
       </c>
       <c r="E6">
-        <v>-10.668</v>
+        <v>-10.185</v>
       </c>
       <c r="F6">
-        <v>1.932</v>
+        <v>2.415</v>
       </c>
       <c r="G6">
         <v>17.5</v>
@@ -1773,45 +1773,45 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M6">
-        <v>0.1000776</v>
+        <v>0.1292025</v>
       </c>
       <c r="N6">
-        <v>0.9785890666666669</v>
+        <v>0.9494641666666669</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.9785890666666669</v>
+        <v>0.9494641666666669</v>
       </c>
       <c r="Q6">
-        <v>0.9915890666666669</v>
+        <v>0.9624641666666669</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08597369685099573</v>
+        <v>0.0863965778704799</v>
       </c>
       <c r="T6">
-        <v>0.7830601268885335</v>
+        <v>0.7913028650663074</v>
       </c>
       <c r="U6">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V6">
         <v>0</v>
       </c>
       <c r="W6">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y6">
-        <v>10.77830270376854</v>
+        <v>8.34865166437698</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08475174897695589</v>
+        <v>0.08487674897695589</v>
       </c>
       <c r="C7">
-        <v>48.76476437626955</v>
+        <v>48.17402842951726</v>
       </c>
       <c r="D7">
-        <v>33.67976437626955</v>
+        <v>33.57202842951726</v>
       </c>
       <c r="E7">
-        <v>-10.185</v>
+        <v>-9.702000000000002</v>
       </c>
       <c r="F7">
-        <v>2.415</v>
+        <v>2.898000000000001</v>
       </c>
       <c r="G7">
         <v>17.5</v>
@@ -1855,45 +1855,45 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M7">
-        <v>0.1292025</v>
+        <v>0.1573614</v>
       </c>
       <c r="N7">
-        <v>0.9494641666666669</v>
+        <v>0.9213052666666668</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>0.9494641666666669</v>
+        <v>0.9213052666666668</v>
       </c>
       <c r="Q7">
-        <v>0.9624641666666669</v>
+        <v>0.9343052666666668</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0863965778704799</v>
+        <v>0.08682845635846373</v>
       </c>
       <c r="T7">
-        <v>0.7913028650663074</v>
+        <v>0.7997209806521193</v>
       </c>
       <c r="U7">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V7">
         <v>0</v>
       </c>
       <c r="W7">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y7">
-        <v>8.34865166437698</v>
+        <v>6.854709392943038</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08487674897695589</v>
+        <v>0.08503174897695591</v>
       </c>
       <c r="C8">
-        <v>48.17402842951726</v>
+        <v>47.55838931598623</v>
       </c>
       <c r="D8">
-        <v>33.57202842951726</v>
+        <v>33.43938931598623</v>
       </c>
       <c r="E8">
-        <v>-9.702000000000002</v>
+        <v>-9.219000000000001</v>
       </c>
       <c r="F8">
-        <v>2.898</v>
+        <v>3.381</v>
       </c>
       <c r="G8">
         <v>17.5</v>
@@ -1937,45 +1937,45 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M8">
-        <v>0.1573614</v>
+        <v>0.1869693</v>
       </c>
       <c r="N8">
-        <v>0.9213052666666669</v>
+        <v>0.8916973666666669</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>0.9213052666666669</v>
+        <v>0.8916973666666669</v>
       </c>
       <c r="Q8">
-        <v>0.9343052666666669</v>
+        <v>0.9046973666666669</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08682845635846373</v>
+        <v>0.08726962255586657</v>
       </c>
       <c r="T8">
-        <v>0.7997209806521193</v>
+        <v>0.808320130981712</v>
       </c>
       <c r="U8">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V8">
         <v>0</v>
       </c>
       <c r="W8">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y8">
-        <v>6.85470939294304</v>
+        <v>5.769218083753144</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0850317489769559</v>
+        <v>0.08512674897695591</v>
       </c>
       <c r="C9">
-        <v>47.55838931598623</v>
+        <v>46.99461116707592</v>
       </c>
       <c r="D9">
-        <v>33.43938931598623</v>
+        <v>33.35861116707592</v>
       </c>
       <c r="E9">
-        <v>-9.219000000000001</v>
+        <v>-8.736000000000001</v>
       </c>
       <c r="F9">
-        <v>3.381000000000001</v>
+        <v>3.864</v>
       </c>
       <c r="G9">
         <v>17.5</v>
@@ -2019,28 +2019,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M9">
-        <v>0.1869693</v>
+        <v>0.2136792</v>
       </c>
       <c r="N9">
-        <v>0.8916973666666669</v>
+        <v>0.8649874666666668</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>0.8916973666666669</v>
+        <v>0.8649874666666668</v>
       </c>
       <c r="Q9">
-        <v>0.9046973666666669</v>
+        <v>0.8779874666666668</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08726962255586657</v>
+        <v>0.08772037932277815</v>
       </c>
       <c r="T9">
-        <v>0.808320130981712</v>
+        <v>0.8171062193619479</v>
       </c>
       <c r="U9">
         <v>0.0553</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>5.769218083753144</v>
+        <v>5.048065823284001</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08512674897695591</v>
+        <v>0.08544674897695591</v>
       </c>
       <c r="C10">
-        <v>46.99461116707592</v>
+        <v>46.24236448610167</v>
       </c>
       <c r="D10">
-        <v>33.35861116707592</v>
+        <v>33.08936448610167</v>
       </c>
       <c r="E10">
-        <v>-8.736000000000001</v>
+        <v>-8.253</v>
       </c>
       <c r="F10">
-        <v>3.864</v>
+        <v>4.347</v>
       </c>
       <c r="G10">
         <v>17.5</v>
@@ -2101,45 +2101,45 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M10">
-        <v>0.2136792</v>
+        <v>0.2512566000000001</v>
       </c>
       <c r="N10">
-        <v>0.8649874666666668</v>
+        <v>0.8274100666666668</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>0.8649874666666668</v>
+        <v>0.8274100666666668</v>
       </c>
       <c r="Q10">
-        <v>0.8779874666666668</v>
+        <v>0.8404100666666668</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08772037932277815</v>
+        <v>0.08818104283181968</v>
       </c>
       <c r="T10">
-        <v>0.8171062193619479</v>
+        <v>0.8260854085857057</v>
       </c>
       <c r="U10">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V10">
         <v>0</v>
       </c>
       <c r="W10">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y10">
-        <v>5.048065823284001</v>
+        <v>4.293087889697889</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08544674897695591</v>
+        <v>0.08591674897695592</v>
       </c>
       <c r="C11">
-        <v>46.24236448610167</v>
+        <v>45.37169595101172</v>
       </c>
       <c r="D11">
-        <v>33.08936448610167</v>
+        <v>32.70169595101171</v>
       </c>
       <c r="E11">
-        <v>-8.253</v>
+        <v>-7.770000000000001</v>
       </c>
       <c r="F11">
-        <v>4.347</v>
+        <v>4.83</v>
       </c>
       <c r="G11">
         <v>17.5</v>
@@ -2183,45 +2183,45 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M11">
-        <v>0.2512566000000001</v>
+        <v>0.296079</v>
       </c>
       <c r="N11">
-        <v>0.8274100666666668</v>
+        <v>0.7825876666666669</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>0.8274100666666668</v>
+        <v>0.7825876666666669</v>
       </c>
       <c r="Q11">
-        <v>0.8404100666666668</v>
+        <v>0.7955876666666669</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08818104283181968</v>
+        <v>0.0886519433077288</v>
       </c>
       <c r="T11">
-        <v>0.8260854085857057</v>
+        <v>0.8352641353477691</v>
       </c>
       <c r="U11">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V11">
         <v>0</v>
       </c>
       <c r="W11">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>4.293087889697889</v>
+        <v>3.643171811126986</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08591674897695592</v>
+        <v>0.08637974897695591</v>
       </c>
       <c r="C12">
-        <v>45.37169595101172</v>
+        <v>44.51558163643288</v>
       </c>
       <c r="D12">
-        <v>32.70169595101171</v>
+        <v>32.32858163643288</v>
       </c>
       <c r="E12">
-        <v>-7.77</v>
+        <v>-7.287000000000001</v>
       </c>
       <c r="F12">
-        <v>4.830000000000001</v>
+        <v>5.313000000000001</v>
       </c>
       <c r="G12">
         <v>17.5</v>
@@ -2265,45 +2265,45 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M12">
-        <v>0.296079</v>
+        <v>0.3405633000000001</v>
       </c>
       <c r="N12">
-        <v>0.7825876666666669</v>
+        <v>0.7381033666666668</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>0.7825876666666669</v>
+        <v>0.7381033666666668</v>
       </c>
       <c r="Q12">
-        <v>0.7955876666666669</v>
+        <v>0.7511033666666668</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.0886519433077288</v>
+        <v>0.08913342581680439</v>
       </c>
       <c r="T12">
-        <v>0.8352641353477691</v>
+        <v>0.8446491256325755</v>
       </c>
       <c r="U12">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V12">
         <v>0</v>
       </c>
       <c r="W12">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y12">
-        <v>3.643171811126986</v>
+        <v>3.167301546193223</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08637974897695591</v>
+        <v>0.08749874897695591</v>
       </c>
       <c r="C13">
-        <v>44.51558163643288</v>
+        <v>43.16503323896993</v>
       </c>
       <c r="D13">
-        <v>32.32858163643288</v>
+        <v>31.46103323896993</v>
       </c>
       <c r="E13">
-        <v>-7.287000000000001</v>
+        <v>-6.804000000000001</v>
       </c>
       <c r="F13">
-        <v>5.313000000000001</v>
+        <v>5.796</v>
       </c>
       <c r="G13">
         <v>17.5</v>
@@ -2347,45 +2347,45 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M13">
-        <v>0.3405633000000001</v>
+        <v>0.4167324000000001</v>
       </c>
       <c r="N13">
-        <v>0.7381033666666668</v>
+        <v>0.6619342666666668</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13">
-        <v>0.7381033666666668</v>
+        <v>0.6619342666666668</v>
       </c>
       <c r="Q13">
-        <v>0.7511033666666668</v>
+        <v>0.6749342666666668</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08913342581680439</v>
+        <v>0.08962585111017717</v>
       </c>
       <c r="T13">
-        <v>0.8446491256325755</v>
+        <v>0.8542474111511273</v>
       </c>
       <c r="U13">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V13">
         <v>0</v>
       </c>
       <c r="W13">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>3.167301546193223</v>
+        <v>2.588391655332455</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08749874897695591</v>
+        <v>0.0882667489769559</v>
       </c>
       <c r="C14">
-        <v>43.16503323896993</v>
+        <v>42.11306871708858</v>
       </c>
       <c r="D14">
-        <v>31.46103323896993</v>
+        <v>30.89206871708858</v>
       </c>
       <c r="E14">
-        <v>-6.804000000000001</v>
+        <v>-6.321000000000001</v>
       </c>
       <c r="F14">
-        <v>5.796</v>
+        <v>6.279000000000001</v>
       </c>
       <c r="G14">
         <v>17.5</v>
@@ -2429,45 +2429,45 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M14">
-        <v>0.4167324000000001</v>
+        <v>0.4759482000000001</v>
       </c>
       <c r="N14">
-        <v>0.6619342666666668</v>
+        <v>0.6027184666666667</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14">
-        <v>0.6619342666666668</v>
+        <v>0.6027184666666667</v>
       </c>
       <c r="Q14">
-        <v>0.6749342666666668</v>
+        <v>0.6157184666666667</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08962585111017717</v>
+        <v>0.09012959652523667</v>
       </c>
       <c r="T14">
-        <v>0.8542474111511273</v>
+        <v>0.8640663469114852</v>
       </c>
       <c r="U14">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V14">
         <v>0</v>
       </c>
       <c r="W14">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y14">
-        <v>2.588391655332455</v>
+        <v>2.266353075117558</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.0882667489769559</v>
+        <v>0.08856674897695591</v>
       </c>
       <c r="C15">
-        <v>42.11306871708858</v>
+        <v>41.41336717121891</v>
       </c>
       <c r="D15">
-        <v>30.89206871708858</v>
+        <v>30.67536717121891</v>
       </c>
       <c r="E15">
-        <v>-6.321000000000001</v>
+        <v>-5.838</v>
       </c>
       <c r="F15">
-        <v>6.279000000000001</v>
+        <v>6.762000000000001</v>
       </c>
       <c r="G15">
         <v>17.5</v>
@@ -2511,28 +2511,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M15">
-        <v>0.4759482000000001</v>
+        <v>0.5125596000000001</v>
       </c>
       <c r="N15">
-        <v>0.6027184666666667</v>
+        <v>0.5661070666666668</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>0.6027184666666667</v>
+        <v>0.5661070666666668</v>
       </c>
       <c r="Q15">
-        <v>0.6157184666666667</v>
+        <v>0.5791070666666668</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09012959652523667</v>
+        <v>0.09064505694994873</v>
       </c>
       <c r="T15">
-        <v>0.8640663469114852</v>
+        <v>0.8741136300151072</v>
       </c>
       <c r="U15">
         <v>0.07580000000000001</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>2.266353075117558</v>
+        <v>2.104470712609161</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08856674897695591</v>
+        <v>0.09099674897695591</v>
       </c>
       <c r="C16">
-        <v>41.41336717121891</v>
+        <v>39.28110823305794</v>
       </c>
       <c r="D16">
-        <v>30.67536717121891</v>
+        <v>29.02610823305794</v>
       </c>
       <c r="E16">
-        <v>-5.838</v>
+        <v>-5.355</v>
       </c>
       <c r="F16">
-        <v>6.762000000000001</v>
+        <v>7.245000000000002</v>
       </c>
       <c r="G16">
         <v>17.5</v>
@@ -2593,45 +2593,45 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M16">
-        <v>0.5125596000000001</v>
+        <v>0.6520500000000001</v>
       </c>
       <c r="N16">
-        <v>0.5661070666666668</v>
+        <v>0.4266166666666668</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>0.5661070666666668</v>
+        <v>0.4266166666666668</v>
       </c>
       <c r="Q16">
-        <v>0.5791070666666668</v>
+        <v>0.4396166666666668</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09064505694994873</v>
+        <v>0.09117264585524225</v>
       </c>
       <c r="T16">
-        <v>0.8741136300151072</v>
+        <v>0.8843973197799908</v>
       </c>
       <c r="U16">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V16">
         <v>0</v>
       </c>
       <c r="W16">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y16">
-        <v>2.104470712609161</v>
+        <v>1.654269866830253</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09099674897695591</v>
+        <v>0.09143874897695591</v>
       </c>
       <c r="C17">
-        <v>39.28110823305794</v>
+        <v>38.51699755131052</v>
       </c>
       <c r="D17">
-        <v>29.02610823305794</v>
+        <v>28.74499755131052</v>
       </c>
       <c r="E17">
-        <v>-5.355000000000001</v>
+        <v>-4.872000000000001</v>
       </c>
       <c r="F17">
-        <v>7.245</v>
+        <v>7.728000000000001</v>
       </c>
       <c r="G17">
         <v>17.5</v>
@@ -2675,28 +2675,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M17">
-        <v>0.65205</v>
+        <v>0.69552</v>
       </c>
       <c r="N17">
-        <v>0.4266166666666669</v>
+        <v>0.3831466666666669</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17">
-        <v>0.4266166666666669</v>
+        <v>0.3831466666666669</v>
       </c>
       <c r="Q17">
-        <v>0.4396166666666669</v>
+        <v>0.3961466666666669</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09117264585524225</v>
+        <v>0.09171279640113798</v>
       </c>
       <c r="T17">
-        <v>0.8843973197799908</v>
+        <v>0.8949258593011811</v>
       </c>
       <c r="U17">
         <v>0.09</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>1.654269866830254</v>
+        <v>1.550878000153363</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09143874897695591</v>
+        <v>0.1015367489769559</v>
       </c>
       <c r="C18">
-        <v>38.51699755131052</v>
+        <v>32.82617702713277</v>
       </c>
       <c r="D18">
-        <v>28.74499755131052</v>
+        <v>23.53717702713277</v>
       </c>
       <c r="E18">
-        <v>-4.872000000000001</v>
+        <v>-4.388999999999999</v>
       </c>
       <c r="F18">
-        <v>7.728000000000001</v>
+        <v>8.211000000000002</v>
       </c>
       <c r="G18">
         <v>17.5</v>
@@ -2757,45 +2757,45 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M18">
-        <v>0.69552</v>
+        <v>1.2053748</v>
       </c>
       <c r="N18">
-        <v>0.3831466666666669</v>
+        <v>-0.1267081333333335</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P18">
-        <v>0.3831466666666669</v>
+        <v>-0.1267081333333335</v>
       </c>
       <c r="Q18">
-        <v>0.3961466666666669</v>
+        <v>-0.1137081333333335</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09171279640113798</v>
+        <v>0.09226596262283845</v>
       </c>
       <c r="T18">
-        <v>0.8949258593011811</v>
+        <v>0.9057080985698701</v>
       </c>
       <c r="U18">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V18">
         <v>0</v>
       </c>
       <c r="W18">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y18">
-        <v>1.550878000153363</v>
+        <v>0.8948807181522846</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1015367489769559</v>
+        <v>0.1025467489769559</v>
       </c>
       <c r="C19">
-        <v>32.82617702713277</v>
+        <v>31.92425349008473</v>
       </c>
       <c r="D19">
-        <v>23.53717702713277</v>
+        <v>23.11825349008473</v>
       </c>
       <c r="E19">
-        <v>-4.388999999999999</v>
+        <v>-3.905999999999999</v>
       </c>
       <c r="F19">
-        <v>8.211000000000002</v>
+        <v>8.694000000000003</v>
       </c>
       <c r="G19">
         <v>17.5</v>
@@ -2839,28 +2839,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M19">
-        <v>1.2053748</v>
+        <v>1.276279200000001</v>
       </c>
       <c r="N19">
-        <v>-0.1267081333333335</v>
+        <v>-0.1976125333333336</v>
       </c>
       <c r="O19">
         <v>-0</v>
       </c>
       <c r="P19">
-        <v>-0.1267081333333335</v>
+        <v>-0.1976125333333336</v>
       </c>
       <c r="Q19">
-        <v>-0.1137081333333335</v>
+        <v>-0.1846125333333336</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09226596262283845</v>
+        <v>0.09283262070360476</v>
       </c>
       <c r="T19">
-        <v>0.9057080985698701</v>
+        <v>0.9167533192841367</v>
       </c>
       <c r="U19">
         <v>0.1468</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.8948807181522846</v>
+        <v>0.8451651226993799</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1025467489769559</v>
+        <v>0.1035567489769559</v>
       </c>
       <c r="C20">
-        <v>31.92425349008472</v>
+        <v>31.03698149696577</v>
       </c>
       <c r="D20">
-        <v>23.11825349008473</v>
+        <v>22.71398149696576</v>
       </c>
       <c r="E20">
-        <v>-3.906000000000001</v>
+        <v>-3.423</v>
       </c>
       <c r="F20">
-        <v>8.694000000000001</v>
+        <v>9.177000000000001</v>
       </c>
       <c r="G20">
         <v>17.5</v>
@@ -2921,28 +2921,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M20">
-        <v>1.2762792</v>
+        <v>1.3471836</v>
       </c>
       <c r="N20">
-        <v>-0.1976125333333334</v>
+        <v>-0.2685169333333335</v>
       </c>
       <c r="O20">
         <v>-0</v>
       </c>
       <c r="P20">
-        <v>-0.1976125333333334</v>
+        <v>-0.2685169333333335</v>
       </c>
       <c r="Q20">
-        <v>-0.1846125333333334</v>
+        <v>-0.2555169333333335</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09283262070360476</v>
+        <v>0.09341327034192087</v>
       </c>
       <c r="T20">
-        <v>0.9167533192841367</v>
+        <v>0.9280712614975211</v>
       </c>
       <c r="U20">
         <v>0.1468</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.84516512269938</v>
+        <v>0.8006827478204653</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1035567489769559</v>
+        <v>0.1153667489769559</v>
       </c>
       <c r="C21">
-        <v>31.03698149696577</v>
+        <v>26.69794214736176</v>
       </c>
       <c r="D21">
-        <v>22.71398149696576</v>
+        <v>18.85794214736177</v>
       </c>
       <c r="E21">
-        <v>-3.423</v>
+        <v>-2.94</v>
       </c>
       <c r="F21">
-        <v>9.177000000000001</v>
+        <v>9.660000000000002</v>
       </c>
       <c r="G21">
         <v>17.5</v>
@@ -3003,45 +3003,45 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M21">
-        <v>1.3471836</v>
+        <v>1.939728</v>
       </c>
       <c r="N21">
-        <v>-0.2685169333333335</v>
+        <v>-0.8610613333333335</v>
       </c>
       <c r="O21">
         <v>-0</v>
       </c>
       <c r="P21">
-        <v>-0.2685169333333335</v>
+        <v>-0.8610613333333335</v>
       </c>
       <c r="Q21">
-        <v>-0.2555169333333335</v>
+        <v>-0.8480613333333334</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09341327034192087</v>
+        <v>0.09400843622119488</v>
       </c>
       <c r="T21">
-        <v>0.9280712614975211</v>
+        <v>0.9396721522662401</v>
       </c>
       <c r="U21">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V21">
         <v>0</v>
       </c>
       <c r="W21">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y21">
-        <v>0.8006827478204653</v>
+        <v>0.5560917132024009</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1153667489769559</v>
+        <v>0.1169167489769559</v>
       </c>
       <c r="C22">
-        <v>26.69794214736176</v>
+        <v>25.80393052564263</v>
       </c>
       <c r="D22">
-        <v>18.85794214736177</v>
+        <v>18.44693052564264</v>
       </c>
       <c r="E22">
-        <v>-2.94</v>
+        <v>-2.456999999999999</v>
       </c>
       <c r="F22">
-        <v>9.660000000000002</v>
+        <v>10.143</v>
       </c>
       <c r="G22">
         <v>17.5</v>
@@ -3085,28 +3085,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M22">
-        <v>1.939728</v>
+        <v>2.036714400000001</v>
       </c>
       <c r="N22">
-        <v>-0.8610613333333335</v>
+        <v>-0.9580477333333337</v>
       </c>
       <c r="O22">
         <v>-0</v>
       </c>
       <c r="P22">
-        <v>-0.8610613333333335</v>
+        <v>-0.9580477333333337</v>
       </c>
       <c r="Q22">
-        <v>-0.8480613333333334</v>
+        <v>-0.9450477333333337</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09400843622119488</v>
+        <v>0.09461866959108343</v>
       </c>
       <c r="T22">
-        <v>0.9396721522662401</v>
+        <v>0.9515667364721421</v>
       </c>
       <c r="U22">
         <v>0.2008</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.5560917132024009</v>
+        <v>0.529611155430858</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1169167489769559</v>
+        <v>0.1184667489769559</v>
       </c>
       <c r="C23">
-        <v>25.80393052564263</v>
+        <v>24.92745286609007</v>
       </c>
       <c r="D23">
-        <v>18.44693052564264</v>
+        <v>18.05345286609008</v>
       </c>
       <c r="E23">
-        <v>-2.457000000000001</v>
+        <v>-1.974</v>
       </c>
       <c r="F23">
-        <v>10.143</v>
+        <v>10.626</v>
       </c>
       <c r="G23">
         <v>17.5</v>
@@ -3167,28 +3167,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M23">
-        <v>2.0367144</v>
+        <v>2.1337008</v>
       </c>
       <c r="N23">
-        <v>-0.9580477333333333</v>
+        <v>-1.055034133333333</v>
       </c>
       <c r="O23">
         <v>-0</v>
       </c>
       <c r="P23">
-        <v>-0.9580477333333333</v>
+        <v>-1.055034133333333</v>
       </c>
       <c r="Q23">
-        <v>-0.9450477333333333</v>
+        <v>-1.042034133333333</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09461866959108343</v>
+        <v>0.09524454997045628</v>
       </c>
       <c r="T23">
-        <v>0.9515667364721421</v>
+        <v>0.9637663100166565</v>
       </c>
       <c r="U23">
         <v>0.2008</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.529611155430858</v>
+        <v>0.5055379210930917</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1184667489769559</v>
+        <v>0.1280667489769559</v>
       </c>
       <c r="C24">
-        <v>24.92745286609007</v>
+        <v>22.33773113866394</v>
       </c>
       <c r="D24">
-        <v>18.05345286609008</v>
+        <v>15.94673113866394</v>
       </c>
       <c r="E24">
-        <v>-1.974</v>
+        <v>-1.491</v>
       </c>
       <c r="F24">
-        <v>10.626</v>
+        <v>11.109</v>
       </c>
       <c r="G24">
         <v>17.5</v>
@@ -3249,45 +3249,45 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M24">
-        <v>2.1337008</v>
+        <v>2.6195022</v>
       </c>
       <c r="N24">
-        <v>-1.055034133333333</v>
+        <v>-1.540835533333333</v>
       </c>
       <c r="O24">
         <v>-0</v>
       </c>
       <c r="P24">
-        <v>-1.055034133333333</v>
+        <v>-1.540835533333333</v>
       </c>
       <c r="Q24">
-        <v>-1.042034133333333</v>
+        <v>-1.527835533333334</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09524454997045628</v>
+        <v>0.09588668698305962</v>
       </c>
       <c r="T24">
-        <v>0.9637663100166565</v>
+        <v>0.9762827556012885</v>
       </c>
       <c r="U24">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V24">
         <v>0</v>
       </c>
       <c r="W24">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y24">
-        <v>0.5055379210930917</v>
+        <v>0.411783073389542</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1280667489769559</v>
+        <v>0.1299667489769559</v>
       </c>
       <c r="C25">
-        <v>22.33773113866394</v>
+        <v>21.49474587688607</v>
       </c>
       <c r="D25">
-        <v>15.94673113866394</v>
+        <v>15.58674587688607</v>
       </c>
       <c r="E25">
-        <v>-1.491</v>
+        <v>-1.007999999999999</v>
       </c>
       <c r="F25">
-        <v>11.109</v>
+        <v>11.592</v>
       </c>
       <c r="G25">
         <v>17.5</v>
@@ -3331,28 +3331,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M25">
-        <v>2.6195022</v>
+        <v>2.733393600000001</v>
       </c>
       <c r="N25">
-        <v>-1.540835533333333</v>
+        <v>-1.654726933333334</v>
       </c>
       <c r="O25">
         <v>-0</v>
       </c>
       <c r="P25">
-        <v>-1.540835533333333</v>
+        <v>-1.654726933333334</v>
       </c>
       <c r="Q25">
-        <v>-1.527835533333334</v>
+        <v>-1.641726933333334</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09588668698305962</v>
+        <v>0.09654572233809988</v>
       </c>
       <c r="T25">
-        <v>0.9762827556012885</v>
+        <v>0.9891285813328845</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.411783073389542</v>
+        <v>0.3946254453316443</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1299667489769559</v>
+        <v>0.1318667489769559</v>
       </c>
       <c r="C26">
-        <v>21.49474587688607</v>
+        <v>20.66765460449454</v>
       </c>
       <c r="D26">
-        <v>15.58674587688607</v>
+        <v>15.24265460449454</v>
       </c>
       <c r="E26">
-        <v>-1.008000000000001</v>
+        <v>-0.5250000000000004</v>
       </c>
       <c r="F26">
-        <v>11.592</v>
+        <v>12.075</v>
       </c>
       <c r="G26">
         <v>17.5</v>
@@ -3413,28 +3413,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M26">
-        <v>2.7333936</v>
+        <v>2.847285</v>
       </c>
       <c r="N26">
-        <v>-1.654726933333333</v>
+        <v>-1.768618333333333</v>
       </c>
       <c r="O26">
         <v>-0</v>
       </c>
       <c r="P26">
-        <v>-1.654726933333333</v>
+        <v>-1.768618333333333</v>
       </c>
       <c r="Q26">
-        <v>-1.641726933333334</v>
+        <v>-1.755618333333334</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09654572233809988</v>
+        <v>0.09722233196927454</v>
       </c>
       <c r="T26">
-        <v>0.9891285813328845</v>
+        <v>1.002316962417323</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.3946254453316445</v>
+        <v>0.3788404275183787</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1318667489769559</v>
+        <v>0.1337667489769559</v>
       </c>
       <c r="C27">
-        <v>20.66765460449454</v>
+        <v>19.85542743530444</v>
       </c>
       <c r="D27">
-        <v>15.24265460449454</v>
+        <v>14.91342743530444</v>
       </c>
       <c r="E27">
-        <v>-0.5250000000000004</v>
+        <v>-0.04199999999999982</v>
       </c>
       <c r="F27">
-        <v>12.075</v>
+        <v>12.558</v>
       </c>
       <c r="G27">
         <v>17.5</v>
@@ -3495,28 +3495,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M27">
-        <v>2.847285</v>
+        <v>2.961176400000001</v>
       </c>
       <c r="N27">
-        <v>-1.768618333333333</v>
+        <v>-1.882509733333334</v>
       </c>
       <c r="O27">
         <v>-0</v>
       </c>
       <c r="P27">
-        <v>-1.768618333333333</v>
+        <v>-1.882509733333334</v>
       </c>
       <c r="Q27">
-        <v>-1.755618333333334</v>
+        <v>-1.869509733333334</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09722233196927454</v>
+        <v>0.09791722834723771</v>
       </c>
       <c r="T27">
-        <v>1.002316962417323</v>
+        <v>1.015861786233773</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.3788404275183787</v>
+        <v>0.3642696418445948</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1337667489769559</v>
+        <v>0.1356667489769559</v>
       </c>
       <c r="C28">
-        <v>19.85542743530444</v>
+        <v>19.0571215802507</v>
       </c>
       <c r="D28">
-        <v>14.91342743530444</v>
+        <v>14.5981215802507</v>
       </c>
       <c r="E28">
-        <v>-0.04199999999999982</v>
+        <v>0.4410000000000007</v>
       </c>
       <c r="F28">
-        <v>12.558</v>
+        <v>13.041</v>
       </c>
       <c r="G28">
         <v>17.5</v>
@@ -3577,28 +3577,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M28">
-        <v>2.961176400000001</v>
+        <v>3.075067800000001</v>
       </c>
       <c r="N28">
-        <v>-1.882509733333334</v>
+        <v>-1.996401133333334</v>
       </c>
       <c r="O28">
         <v>-0</v>
       </c>
       <c r="P28">
-        <v>-1.882509733333334</v>
+        <v>-1.996401133333334</v>
       </c>
       <c r="Q28">
-        <v>-1.869509733333334</v>
+        <v>-1.983401133333334</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09791722834723771</v>
+        <v>0.09863116298213138</v>
       </c>
       <c r="T28">
-        <v>1.015861786233773</v>
+        <v>1.029777701113688</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.3642696418445948</v>
+        <v>0.3507781736281284</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1356667489769559</v>
+        <v>0.1375667489769559</v>
       </c>
       <c r="C29">
-        <v>19.0571215802507</v>
+        <v>18.2718723308037</v>
       </c>
       <c r="D29">
-        <v>14.5981215802507</v>
+        <v>14.2958723308037</v>
       </c>
       <c r="E29">
-        <v>0.4410000000000007</v>
+        <v>0.9240000000000013</v>
       </c>
       <c r="F29">
-        <v>13.041</v>
+        <v>13.524</v>
       </c>
       <c r="G29">
         <v>17.5</v>
@@ -3659,28 +3659,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M29">
-        <v>3.075067800000001</v>
+        <v>3.188959200000001</v>
       </c>
       <c r="N29">
-        <v>-1.996401133333334</v>
+        <v>-2.110292533333334</v>
       </c>
       <c r="O29">
         <v>-0</v>
       </c>
       <c r="P29">
-        <v>-1.996401133333334</v>
+        <v>-2.110292533333334</v>
       </c>
       <c r="Q29">
-        <v>-1.983401133333334</v>
+        <v>-2.097292533333334</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09863116298213138</v>
+        <v>0.09936492913466098</v>
       </c>
       <c r="T29">
-        <v>1.029777701113688</v>
+        <v>1.044080169184711</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.3507781736281284</v>
+        <v>0.3382503817128381</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1375667489769559</v>
+        <v>0.1394667489769559</v>
       </c>
       <c r="C30">
-        <v>18.2718723308037</v>
+        <v>17.49888513977596</v>
       </c>
       <c r="D30">
-        <v>14.2958723308037</v>
+        <v>14.00588513977597</v>
       </c>
       <c r="E30">
-        <v>0.9240000000000013</v>
+        <v>1.407000000000002</v>
       </c>
       <c r="F30">
-        <v>13.524</v>
+        <v>14.007</v>
       </c>
       <c r="G30">
         <v>17.5</v>
@@ -3741,28 +3741,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M30">
-        <v>3.188959200000001</v>
+        <v>3.302850600000001</v>
       </c>
       <c r="N30">
-        <v>-2.110292533333334</v>
+        <v>-2.224183933333334</v>
       </c>
       <c r="O30">
         <v>-0</v>
       </c>
       <c r="P30">
-        <v>-2.110292533333334</v>
+        <v>-2.224183933333334</v>
       </c>
       <c r="Q30">
-        <v>-2.097292533333334</v>
+        <v>-2.211183933333334</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09936492913466098</v>
+        <v>0.1001193647562759</v>
       </c>
       <c r="T30">
-        <v>1.044080169184711</v>
+        <v>1.058785523680271</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.3382503817128381</v>
+        <v>0.3265865754468781</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1394667489769559</v>
+        <v>0.1413667489769559</v>
       </c>
       <c r="C31">
-        <v>17.49888513977597</v>
+        <v>16.73742864679648</v>
       </c>
       <c r="D31">
-        <v>14.00588513977597</v>
+        <v>13.72742864679648</v>
       </c>
       <c r="E31">
-        <v>1.406999999999998</v>
+        <v>1.889999999999999</v>
       </c>
       <c r="F31">
-        <v>14.007</v>
+        <v>14.49</v>
       </c>
       <c r="G31">
         <v>17.5</v>
@@ -3823,28 +3823,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M31">
-        <v>3.3028506</v>
+        <v>3.416742</v>
       </c>
       <c r="N31">
-        <v>-2.224183933333333</v>
+        <v>-2.338075333333333</v>
       </c>
       <c r="O31">
         <v>-0</v>
       </c>
       <c r="P31">
-        <v>-2.224183933333333</v>
+        <v>-2.338075333333333</v>
       </c>
       <c r="Q31">
-        <v>-2.211183933333333</v>
+        <v>-2.325075333333333</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1001193647562759</v>
+        <v>0.1008953556813656</v>
       </c>
       <c r="T31">
-        <v>1.058785523680271</v>
+        <v>1.073911031161417</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.3265865754468782</v>
+        <v>0.3157003562653156</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1413667489769559</v>
+        <v>0.1432667489769559</v>
       </c>
       <c r="C32">
-        <v>16.73742864679648</v>
+        <v>15.98682851954611</v>
       </c>
       <c r="D32">
-        <v>13.72742864679648</v>
+        <v>13.45982851954611</v>
       </c>
       <c r="E32">
-        <v>1.889999999999999</v>
+        <v>2.372999999999999</v>
       </c>
       <c r="F32">
-        <v>14.49</v>
+        <v>14.973</v>
       </c>
       <c r="G32">
         <v>17.5</v>
@@ -3905,28 +3905,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M32">
-        <v>3.416742</v>
+        <v>3.5306334</v>
       </c>
       <c r="N32">
-        <v>-2.338075333333333</v>
+        <v>-2.451966733333333</v>
       </c>
       <c r="O32">
         <v>-0</v>
       </c>
       <c r="P32">
-        <v>-2.338075333333333</v>
+        <v>-2.451966733333333</v>
       </c>
       <c r="Q32">
-        <v>-2.325075333333333</v>
+        <v>-2.438966733333333</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1008953556813656</v>
+        <v>0.1016938390970376</v>
       </c>
       <c r="T32">
-        <v>1.073911031161417</v>
+        <v>1.089474959149264</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.3157003562653156</v>
+        <v>0.3055164738051441</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1432667489769559</v>
+        <v>0.1451667489769559</v>
       </c>
       <c r="C33">
-        <v>15.98682851954611</v>
+        <v>15.24646200156665</v>
       </c>
       <c r="D33">
-        <v>13.45982851954611</v>
+        <v>13.20246200156665</v>
       </c>
       <c r="E33">
-        <v>2.372999999999999</v>
+        <v>2.856</v>
       </c>
       <c r="F33">
-        <v>14.973</v>
+        <v>15.456</v>
       </c>
       <c r="G33">
         <v>17.5</v>
@@ -3987,28 +3987,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M33">
-        <v>3.5306334</v>
+        <v>3.644524800000001</v>
       </c>
       <c r="N33">
-        <v>-2.451966733333333</v>
+        <v>-2.565858133333334</v>
       </c>
       <c r="O33">
         <v>-0</v>
       </c>
       <c r="P33">
-        <v>-2.451966733333333</v>
+        <v>-2.565858133333334</v>
       </c>
       <c r="Q33">
-        <v>-2.438966733333333</v>
+        <v>-2.552858133333334</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1016938390970376</v>
+        <v>0.1025158073190528</v>
       </c>
       <c r="T33">
-        <v>1.089474959149264</v>
+        <v>1.105496649724989</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.3055164738051441</v>
+        <v>0.2959690839987333</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1451667489769559</v>
+        <v>0.1470667489769559</v>
       </c>
       <c r="C34">
-        <v>15.24646200156665</v>
+        <v>14.51575307384463</v>
       </c>
       <c r="D34">
-        <v>13.20246200156665</v>
+        <v>12.95475307384464</v>
       </c>
       <c r="E34">
-        <v>2.856</v>
+        <v>3.339</v>
       </c>
       <c r="F34">
-        <v>15.456</v>
+        <v>15.939</v>
       </c>
       <c r="G34">
         <v>17.5</v>
@@ -4069,28 +4069,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M34">
-        <v>3.644524800000001</v>
+        <v>3.758416200000001</v>
       </c>
       <c r="N34">
-        <v>-2.565858133333334</v>
+        <v>-2.679749533333334</v>
       </c>
       <c r="O34">
         <v>-0</v>
       </c>
       <c r="P34">
-        <v>-2.565858133333334</v>
+        <v>-2.679749533333334</v>
       </c>
       <c r="Q34">
-        <v>-2.552858133333334</v>
+        <v>-2.666749533333334</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1025158073190528</v>
+        <v>0.1033623119059043</v>
       </c>
       <c r="T34">
-        <v>1.105496649724989</v>
+        <v>1.121996599720884</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.2959690839987333</v>
+        <v>0.2870003238775596</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1470667489769559</v>
+        <v>0.1489667489769559</v>
       </c>
       <c r="C35">
-        <v>14.51575307384463</v>
+        <v>13.79416815104356</v>
       </c>
       <c r="D35">
-        <v>12.95475307384464</v>
+        <v>12.71616815104356</v>
       </c>
       <c r="E35">
-        <v>3.339</v>
+        <v>3.822000000000003</v>
       </c>
       <c r="F35">
-        <v>15.939</v>
+        <v>16.422</v>
       </c>
       <c r="G35">
         <v>17.5</v>
@@ -4151,28 +4151,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M35">
-        <v>3.758416200000001</v>
+        <v>3.872307600000001</v>
       </c>
       <c r="N35">
-        <v>-2.679749533333334</v>
+        <v>-2.793640933333334</v>
       </c>
       <c r="O35">
         <v>-0</v>
       </c>
       <c r="P35">
-        <v>-2.679749533333334</v>
+        <v>-2.793640933333334</v>
       </c>
       <c r="Q35">
-        <v>-2.666749533333334</v>
+        <v>-2.780640933333334</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1033623119059043</v>
+        <v>0.1042344681469029</v>
       </c>
       <c r="T35">
-        <v>1.121996599720884</v>
+        <v>1.138996548201503</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.2870003238775596</v>
+        <v>0.2785591378811607</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1489667489769559</v>
+        <v>0.1508667489769559</v>
       </c>
       <c r="C36">
-        <v>13.79416815104356</v>
+        <v>13.08121224470556</v>
       </c>
       <c r="D36">
-        <v>12.71616815104356</v>
+        <v>12.48621224470556</v>
       </c>
       <c r="E36">
-        <v>3.822000000000003</v>
+        <v>4.305000000000003</v>
       </c>
       <c r="F36">
-        <v>16.422</v>
+        <v>16.905</v>
       </c>
       <c r="G36">
         <v>17.5</v>
@@ -4233,28 +4233,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M36">
-        <v>3.872307600000001</v>
+        <v>3.986199000000001</v>
       </c>
       <c r="N36">
-        <v>-2.793640933333334</v>
+        <v>-2.907532333333334</v>
       </c>
       <c r="O36">
         <v>-0</v>
       </c>
       <c r="P36">
-        <v>-2.793640933333334</v>
+        <v>-2.907532333333334</v>
       </c>
       <c r="Q36">
-        <v>-2.780640933333334</v>
+        <v>-2.894532333333335</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1042344681469029</v>
+        <v>0.1051334599645476</v>
       </c>
       <c r="T36">
-        <v>1.138996548201503</v>
+        <v>1.156519572019988</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.2785591378811607</v>
+        <v>0.2706003053702704</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1508667489769559</v>
+        <v>0.1527667489769559</v>
       </c>
       <c r="C37">
-        <v>13.08121224470556</v>
+        <v>12.37642553536048</v>
       </c>
       <c r="D37">
-        <v>12.48621224470556</v>
+        <v>12.26442553536048</v>
       </c>
       <c r="E37">
-        <v>4.305000000000003</v>
+        <v>4.788000000000004</v>
       </c>
       <c r="F37">
-        <v>16.905</v>
+        <v>17.38800000000001</v>
       </c>
       <c r="G37">
         <v>17.5</v>
@@ -4315,28 +4315,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M37">
-        <v>3.986199000000001</v>
+        <v>4.100090400000002</v>
       </c>
       <c r="N37">
-        <v>-2.907532333333334</v>
+        <v>-3.021423733333335</v>
       </c>
       <c r="O37">
         <v>-0</v>
       </c>
       <c r="P37">
-        <v>-2.907532333333334</v>
+        <v>-3.021423733333335</v>
       </c>
       <c r="Q37">
-        <v>-2.894532333333335</v>
+        <v>-3.008423733333335</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1051334599645476</v>
+        <v>0.1060605452764936</v>
       </c>
       <c r="T37">
-        <v>1.156519572019988</v>
+        <v>1.1745901903328</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.2706003053702704</v>
+        <v>0.2630836302210962</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1527667489769559</v>
+        <v>0.1546667489769559</v>
       </c>
       <c r="C38">
-        <v>12.37642553536048</v>
+        <v>11.67938030358712</v>
       </c>
       <c r="D38">
-        <v>12.26442553536048</v>
+        <v>12.05038030358712</v>
       </c>
       <c r="E38">
-        <v>4.788</v>
+        <v>5.271000000000001</v>
       </c>
       <c r="F38">
-        <v>17.388</v>
+        <v>17.871</v>
       </c>
       <c r="G38">
         <v>17.5</v>
@@ -4397,28 +4397,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M38">
-        <v>4.100090400000001</v>
+        <v>4.213981800000001</v>
       </c>
       <c r="N38">
-        <v>-3.021423733333334</v>
+        <v>-3.135315133333334</v>
       </c>
       <c r="O38">
         <v>-0</v>
       </c>
       <c r="P38">
-        <v>-3.021423733333334</v>
+        <v>-3.135315133333334</v>
       </c>
       <c r="Q38">
-        <v>-3.008423733333334</v>
+        <v>-3.122315133333334</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1060605452764936</v>
+        <v>0.107017061868184</v>
       </c>
       <c r="T38">
-        <v>1.1745901903328</v>
+        <v>1.193234479068242</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.2630836302210963</v>
+        <v>0.2559732618367423</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1546667489769559</v>
+        <v>0.1565667489769559</v>
       </c>
       <c r="C39">
-        <v>11.67938030358712</v>
+        <v>10.98967817692654</v>
       </c>
       <c r="D39">
-        <v>12.05038030358712</v>
+        <v>11.84367817692654</v>
       </c>
       <c r="E39">
-        <v>5.271000000000001</v>
+        <v>5.754000000000001</v>
       </c>
       <c r="F39">
-        <v>17.871</v>
+        <v>18.354</v>
       </c>
       <c r="G39">
         <v>17.5</v>
@@ -4479,28 +4479,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M39">
-        <v>4.213981800000001</v>
+        <v>4.327873200000001</v>
       </c>
       <c r="N39">
-        <v>-3.135315133333334</v>
+        <v>-3.249206533333334</v>
       </c>
       <c r="O39">
         <v>-0</v>
       </c>
       <c r="P39">
-        <v>-3.135315133333334</v>
+        <v>-3.249206533333334</v>
       </c>
       <c r="Q39">
-        <v>-3.122315133333334</v>
+        <v>-3.236206533333334</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.107017061868184</v>
+        <v>0.1080044338337998</v>
       </c>
       <c r="T39">
-        <v>1.193234479068242</v>
+        <v>1.212480196472568</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.2559732618367423</v>
+        <v>0.2492371233673544</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1565667489769559</v>
+        <v>0.1584667489769559</v>
       </c>
       <c r="C40">
-        <v>10.98967817692654</v>
+        <v>10.30694765536189</v>
       </c>
       <c r="D40">
-        <v>11.84367817692654</v>
+        <v>11.64394765536189</v>
       </c>
       <c r="E40">
-        <v>5.754000000000001</v>
+        <v>6.237000000000002</v>
       </c>
       <c r="F40">
-        <v>18.354</v>
+        <v>18.837</v>
       </c>
       <c r="G40">
         <v>17.5</v>
@@ -4561,28 +4561,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M40">
-        <v>4.327873200000001</v>
+        <v>4.441764600000001</v>
       </c>
       <c r="N40">
-        <v>-3.249206533333334</v>
+        <v>-3.363097933333334</v>
       </c>
       <c r="O40">
         <v>-0</v>
       </c>
       <c r="P40">
-        <v>-3.249206533333334</v>
+        <v>-3.363097933333334</v>
       </c>
       <c r="Q40">
-        <v>-3.236206533333334</v>
+        <v>-3.350097933333334</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1080044338337998</v>
+        <v>0.1090241786507474</v>
       </c>
       <c r="T40">
-        <v>1.212480196472568</v>
+        <v>1.232356921004905</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.2492371233673544</v>
+        <v>0.2428464278963965</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1584667489769559</v>
+        <v>0.1603667489769559</v>
       </c>
       <c r="C41">
-        <v>10.30694765536189</v>
+        <v>9.630841883026172</v>
       </c>
       <c r="D41">
-        <v>11.64394765536189</v>
+        <v>11.45084188302618</v>
       </c>
       <c r="E41">
-        <v>6.237000000000002</v>
+        <v>6.720000000000002</v>
       </c>
       <c r="F41">
-        <v>18.837</v>
+        <v>19.32</v>
       </c>
       <c r="G41">
         <v>17.5</v>
@@ -4643,28 +4643,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M41">
-        <v>4.441764600000001</v>
+        <v>4.555656000000001</v>
       </c>
       <c r="N41">
-        <v>-3.363097933333334</v>
+        <v>-3.476989333333334</v>
       </c>
       <c r="O41">
         <v>-0</v>
       </c>
       <c r="P41">
-        <v>-3.363097933333334</v>
+        <v>-3.476989333333334</v>
       </c>
       <c r="Q41">
-        <v>-3.350097933333334</v>
+        <v>-3.463989333333334</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1090241786507474</v>
+        <v>0.1100779149615932</v>
       </c>
       <c r="T41">
-        <v>1.232356921004905</v>
+        <v>1.252896203021654</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.2428464278963965</v>
+        <v>0.2367752671989867</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1603667489769559</v>
+        <v>0.1622667489769559</v>
       </c>
       <c r="C42">
-        <v>9.630841883026172</v>
+        <v>8.961036638019678</v>
       </c>
       <c r="D42">
-        <v>11.45084188302618</v>
+        <v>11.26403663801968</v>
       </c>
       <c r="E42">
-        <v>6.720000000000002</v>
+        <v>7.203000000000003</v>
       </c>
       <c r="F42">
-        <v>19.32</v>
+        <v>19.803</v>
       </c>
       <c r="G42">
         <v>17.5</v>
@@ -4725,28 +4725,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M42">
-        <v>4.555656000000001</v>
+        <v>4.669547400000001</v>
       </c>
       <c r="N42">
-        <v>-3.476989333333334</v>
+        <v>-3.590880733333334</v>
       </c>
       <c r="O42">
         <v>-0</v>
       </c>
       <c r="P42">
-        <v>-3.476989333333334</v>
+        <v>-3.590880733333334</v>
       </c>
       <c r="Q42">
-        <v>-3.463989333333334</v>
+        <v>-3.577880733333334</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1100779149615932</v>
+        <v>0.1111673711473829</v>
       </c>
       <c r="T42">
-        <v>1.252896203021654</v>
+        <v>1.274131731886427</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.2367752671989867</v>
+        <v>0.2310002606819382</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1622667489769559</v>
+        <v>0.1641667489769559</v>
       </c>
       <c r="C43">
-        <v>8.961036638019678</v>
+        <v>8.297228515829854</v>
       </c>
       <c r="D43">
-        <v>11.26403663801968</v>
+        <v>11.08322851582986</v>
       </c>
       <c r="E43">
-        <v>7.203000000000003</v>
+        <v>7.686000000000003</v>
       </c>
       <c r="F43">
-        <v>19.803</v>
+        <v>20.286</v>
       </c>
       <c r="G43">
         <v>17.5</v>
@@ -4807,28 +4807,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M43">
-        <v>4.669547400000001</v>
+        <v>4.783438800000002</v>
       </c>
       <c r="N43">
-        <v>-3.590880733333334</v>
+        <v>-3.704772133333335</v>
       </c>
       <c r="O43">
         <v>-0</v>
       </c>
       <c r="P43">
-        <v>-3.590880733333334</v>
+        <v>-3.704772133333335</v>
       </c>
       <c r="Q43">
-        <v>-3.577880733333334</v>
+        <v>-3.691772133333335</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1111673711473829</v>
+        <v>0.112294394787855</v>
       </c>
       <c r="T43">
-        <v>1.274131731886427</v>
+        <v>1.296099520367228</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.2310002606819382</v>
+        <v>0.2255002544752254</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1641667489769559</v>
+        <v>0.1660667489769559</v>
       </c>
       <c r="C44">
-        <v>8.297228515829858</v>
+        <v>7.639133284943458</v>
       </c>
       <c r="D44">
-        <v>11.08322851582986</v>
+        <v>10.90813328494346</v>
       </c>
       <c r="E44">
-        <v>7.686</v>
+        <v>8.169</v>
       </c>
       <c r="F44">
-        <v>20.286</v>
+        <v>20.769</v>
       </c>
       <c r="G44">
         <v>17.5</v>
@@ -4889,28 +4889,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M44">
-        <v>4.783438800000001</v>
+        <v>4.897330200000001</v>
       </c>
       <c r="N44">
-        <v>-3.704772133333334</v>
+        <v>-3.818663533333334</v>
       </c>
       <c r="O44">
         <v>-0</v>
       </c>
       <c r="P44">
-        <v>-3.704772133333334</v>
+        <v>-3.818663533333334</v>
       </c>
       <c r="Q44">
-        <v>-3.691772133333334</v>
+        <v>-3.805663533333334</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.112294394787855</v>
+        <v>0.1134609631174665</v>
       </c>
       <c r="T44">
-        <v>1.296099520367228</v>
+        <v>1.318838108443846</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.2255002544752254</v>
+        <v>0.2202560625106853</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1660667489769559</v>
+        <v>0.1679667489769559</v>
       </c>
       <c r="C45">
-        <v>7.639133284943458</v>
+        <v>6.986484395904903</v>
       </c>
       <c r="D45">
-        <v>10.90813328494346</v>
+        <v>10.7384843959049</v>
       </c>
       <c r="E45">
-        <v>8.169</v>
+        <v>8.652000000000001</v>
       </c>
       <c r="F45">
-        <v>20.769</v>
+        <v>21.252</v>
       </c>
       <c r="G45">
         <v>17.5</v>
@@ -4971,28 +4971,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M45">
-        <v>4.897330200000001</v>
+        <v>5.011221600000001</v>
       </c>
       <c r="N45">
-        <v>-3.818663533333334</v>
+        <v>-3.932554933333334</v>
       </c>
       <c r="O45">
         <v>-0</v>
       </c>
       <c r="P45">
-        <v>-3.818663533333334</v>
+        <v>-3.932554933333334</v>
       </c>
       <c r="Q45">
-        <v>-3.805663533333334</v>
+        <v>-3.919554933333334</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1134609631174665</v>
+        <v>0.114669194601707</v>
       </c>
       <c r="T45">
-        <v>1.318838108443846</v>
+        <v>1.342388788951772</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.2202560625106853</v>
+        <v>0.2152502429081696</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1679667489769559</v>
+        <v>0.1698667489769559</v>
       </c>
       <c r="C46">
-        <v>6.986484395904903</v>
+        <v>6.339031627371337</v>
       </c>
       <c r="D46">
-        <v>10.7384843959049</v>
+        <v>10.57403162737134</v>
       </c>
       <c r="E46">
-        <v>8.652000000000001</v>
+        <v>9.135000000000002</v>
       </c>
       <c r="F46">
-        <v>21.252</v>
+        <v>21.735</v>
       </c>
       <c r="G46">
         <v>17.5</v>
@@ -5053,28 +5053,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M46">
-        <v>5.011221600000001</v>
+        <v>5.125113000000001</v>
       </c>
       <c r="N46">
-        <v>-3.932554933333334</v>
+        <v>-4.046446333333334</v>
       </c>
       <c r="O46">
         <v>-0</v>
       </c>
       <c r="P46">
-        <v>-3.932554933333334</v>
+        <v>-4.046446333333334</v>
       </c>
       <c r="Q46">
-        <v>-3.919554933333334</v>
+        <v>-4.033446333333334</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.114669194601707</v>
+        <v>0.1159213617762835</v>
       </c>
       <c r="T46">
-        <v>1.342388788951772</v>
+        <v>1.366795857841804</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.2152502429081696</v>
+        <v>0.2104669041768771</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1698667489769559</v>
+        <v>0.1717667489769559</v>
       </c>
       <c r="C47">
-        <v>6.339031627371337</v>
+        <v>5.696539854699797</v>
       </c>
       <c r="D47">
-        <v>10.57403162737134</v>
+        <v>10.4145398546998</v>
       </c>
       <c r="E47">
-        <v>9.135000000000002</v>
+        <v>9.618000000000002</v>
       </c>
       <c r="F47">
-        <v>21.735</v>
+        <v>22.218</v>
       </c>
       <c r="G47">
         <v>17.5</v>
@@ -5135,28 +5135,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M47">
-        <v>5.125113000000001</v>
+        <v>5.239004400000001</v>
       </c>
       <c r="N47">
-        <v>-4.046446333333334</v>
+        <v>-4.160337733333334</v>
       </c>
       <c r="O47">
         <v>-0</v>
       </c>
       <c r="P47">
-        <v>-4.046446333333334</v>
+        <v>-4.160337733333334</v>
       </c>
       <c r="Q47">
-        <v>-4.033446333333334</v>
+        <v>-4.147337733333334</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1159213617762835</v>
+        <v>0.1172199055128813</v>
       </c>
       <c r="T47">
-        <v>1.366795857841804</v>
+        <v>1.392106892246282</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.2104669041768771</v>
+        <v>0.205891536694771</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1717667489769559</v>
+        <v>0.1736667489769559</v>
       </c>
       <c r="C48">
-        <v>5.696539854699797</v>
+        <v>5.058787928321376</v>
       </c>
       <c r="D48">
-        <v>10.4145398546998</v>
+        <v>10.25978792832138</v>
       </c>
       <c r="E48">
-        <v>9.618000000000002</v>
+        <v>10.101</v>
       </c>
       <c r="F48">
-        <v>22.218</v>
+        <v>22.701</v>
       </c>
       <c r="G48">
         <v>17.5</v>
@@ -5217,28 +5217,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M48">
-        <v>5.239004400000001</v>
+        <v>5.352895800000002</v>
       </c>
       <c r="N48">
-        <v>-4.160337733333334</v>
+        <v>-4.274229133333335</v>
       </c>
       <c r="O48">
         <v>-0</v>
       </c>
       <c r="P48">
-        <v>-4.160337733333334</v>
+        <v>-4.274229133333335</v>
       </c>
       <c r="Q48">
-        <v>-4.147337733333334</v>
+        <v>-4.261229133333335</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1172199055128813</v>
+        <v>0.1185674508999168</v>
       </c>
       <c r="T48">
-        <v>1.392106892246282</v>
+        <v>1.418373060024513</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.205891536694771</v>
+        <v>0.2015108657012652</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1736667489769559</v>
+        <v>0.1755667489769559</v>
       </c>
       <c r="C49">
-        <v>5.058787928321376</v>
+        <v>4.425567650650152</v>
       </c>
       <c r="D49">
-        <v>10.25978792832138</v>
+        <v>10.10956765065015</v>
       </c>
       <c r="E49">
-        <v>10.101</v>
+        <v>10.584</v>
       </c>
       <c r="F49">
-        <v>22.701</v>
+        <v>23.184</v>
       </c>
       <c r="G49">
         <v>17.5</v>
@@ -5299,28 +5299,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M49">
-        <v>5.352895800000002</v>
+        <v>5.466787200000002</v>
       </c>
       <c r="N49">
-        <v>-4.274229133333335</v>
+        <v>-4.388120533333335</v>
       </c>
       <c r="O49">
         <v>-0</v>
       </c>
       <c r="P49">
-        <v>-4.274229133333335</v>
+        <v>-4.388120533333335</v>
       </c>
       <c r="Q49">
-        <v>-4.261229133333335</v>
+        <v>-4.375120533333335</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1185674508999168</v>
+        <v>0.1199668249556844</v>
       </c>
       <c r="T49">
-        <v>1.418373060024513</v>
+        <v>1.445649465024985</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.2015108657012652</v>
+        <v>0.1973127226658222</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1755667489769559</v>
+        <v>0.1774667489769559</v>
       </c>
       <c r="C50">
-        <v>4.425567650650155</v>
+        <v>3.796682841573592</v>
       </c>
       <c r="D50">
-        <v>10.10956765065016</v>
+        <v>9.963682841573592</v>
       </c>
       <c r="E50">
-        <v>10.584</v>
+        <v>11.067</v>
       </c>
       <c r="F50">
-        <v>23.184</v>
+        <v>23.667</v>
       </c>
       <c r="G50">
         <v>17.5</v>
@@ -5381,28 +5381,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M50">
-        <v>5.466787200000001</v>
+        <v>5.580678600000001</v>
       </c>
       <c r="N50">
-        <v>-4.388120533333334</v>
+        <v>-4.502011933333334</v>
       </c>
       <c r="O50">
         <v>-0</v>
       </c>
       <c r="P50">
-        <v>-4.388120533333334</v>
+        <v>-4.502011933333334</v>
       </c>
       <c r="Q50">
-        <v>-4.375120533333334</v>
+        <v>-4.489011933333334</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1199668249556844</v>
+        <v>0.1214210764254037</v>
       </c>
       <c r="T50">
-        <v>1.445649465024985</v>
+        <v>1.473995532966651</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.1973127226658222</v>
+        <v>0.193285932407336</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1774667489769559</v>
+        <v>0.1793667489769559</v>
       </c>
       <c r="C51">
-        <v>3.796682841573592</v>
+        <v>3.171948483703904</v>
       </c>
       <c r="D51">
-        <v>9.963682841573592</v>
+        <v>9.821948483703908</v>
       </c>
       <c r="E51">
-        <v>11.067</v>
+        <v>11.55</v>
       </c>
       <c r="F51">
-        <v>23.667</v>
+        <v>24.15</v>
       </c>
       <c r="G51">
         <v>17.5</v>
@@ -5463,28 +5463,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M51">
-        <v>5.580678600000001</v>
+        <v>5.694570000000001</v>
       </c>
       <c r="N51">
-        <v>-4.502011933333334</v>
+        <v>-4.615903333333334</v>
       </c>
       <c r="O51">
         <v>-0</v>
       </c>
       <c r="P51">
-        <v>-4.502011933333334</v>
+        <v>-4.615903333333334</v>
       </c>
       <c r="Q51">
-        <v>-4.489011933333334</v>
+        <v>-4.602903333333334</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1214210764254037</v>
+        <v>0.1229334979539118</v>
       </c>
       <c r="T51">
-        <v>1.473995532966651</v>
+        <v>1.503475443625984</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.193285932407336</v>
+        <v>0.1894202137591894</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1793667489769559</v>
+        <v>0.1812667489769559</v>
       </c>
       <c r="C52">
-        <v>3.171948483703904</v>
+        <v>2.551189939559528</v>
       </c>
       <c r="D52">
-        <v>9.821948483703908</v>
+        <v>9.684189939559531</v>
       </c>
       <c r="E52">
-        <v>11.55</v>
+        <v>12.033</v>
       </c>
       <c r="F52">
-        <v>24.15</v>
+        <v>24.633</v>
       </c>
       <c r="G52">
         <v>17.5</v>
@@ -5545,28 +5545,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M52">
-        <v>5.694570000000001</v>
+        <v>5.808461400000001</v>
       </c>
       <c r="N52">
-        <v>-4.615903333333334</v>
+        <v>-4.729794733333334</v>
       </c>
       <c r="O52">
         <v>-0</v>
       </c>
       <c r="P52">
-        <v>-4.615903333333334</v>
+        <v>-4.729794733333334</v>
       </c>
       <c r="Q52">
-        <v>-4.602903333333334</v>
+        <v>-4.716794733333334</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1229334979539118</v>
+        <v>0.1245076509733794</v>
       </c>
       <c r="T52">
-        <v>1.503475443625984</v>
+        <v>1.534158615944882</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.1894202137591894</v>
+        <v>0.1857060919207738</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1812667489769559</v>
+        <v>0.1831667489769559</v>
       </c>
       <c r="C53">
-        <v>2.551189939559528</v>
+        <v>1.93424223371224</v>
       </c>
       <c r="D53">
-        <v>9.684189939559531</v>
+        <v>9.550242233712243</v>
       </c>
       <c r="E53">
-        <v>12.033</v>
+        <v>12.516</v>
       </c>
       <c r="F53">
-        <v>24.633</v>
+        <v>25.116</v>
       </c>
       <c r="G53">
         <v>17.5</v>
@@ -5627,28 +5627,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M53">
-        <v>5.808461400000001</v>
+        <v>5.922352800000001</v>
       </c>
       <c r="N53">
-        <v>-4.729794733333334</v>
+        <v>-4.843686133333335</v>
       </c>
       <c r="O53">
         <v>-0</v>
       </c>
       <c r="P53">
-        <v>-4.729794733333334</v>
+        <v>-4.843686133333335</v>
       </c>
       <c r="Q53">
-        <v>-4.716794733333334</v>
+        <v>-4.830686133333335</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1245076509733794</v>
+        <v>0.1261473937019915</v>
       </c>
       <c r="T53">
-        <v>1.534158615944882</v>
+        <v>1.566120253777067</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.1857060919207738</v>
+        <v>0.1821348209222974</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1831667489769559</v>
+        <v>0.1850667489769559</v>
       </c>
       <c r="C54">
-        <v>1.93424223371224</v>
+        <v>1.32094939369588</v>
       </c>
       <c r="D54">
-        <v>9.550242233712243</v>
+        <v>9.419949393695884</v>
       </c>
       <c r="E54">
-        <v>12.516</v>
+        <v>12.999</v>
       </c>
       <c r="F54">
-        <v>25.116</v>
+        <v>25.599</v>
       </c>
       <c r="G54">
         <v>17.5</v>
@@ -5709,28 +5709,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M54">
-        <v>5.922352800000001</v>
+        <v>6.036244200000001</v>
       </c>
       <c r="N54">
-        <v>-4.843686133333335</v>
+        <v>-4.957577533333335</v>
       </c>
       <c r="O54">
         <v>-0</v>
       </c>
       <c r="P54">
-        <v>-4.843686133333335</v>
+        <v>-4.957577533333335</v>
       </c>
       <c r="Q54">
-        <v>-4.830686133333335</v>
+        <v>-4.944577533333335</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1261473937019915</v>
+        <v>0.1278569127169275</v>
       </c>
       <c r="T54">
-        <v>1.566120253777067</v>
+        <v>1.599441961304239</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.1821348209222974</v>
+        <v>0.1786983148671597</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1850667489769559</v>
+        <v>0.1869667489769559</v>
       </c>
       <c r="C55">
-        <v>1.32094939369588</v>
+        <v>0.7111638441402697</v>
       </c>
       <c r="D55">
-        <v>9.419949393695884</v>
+        <v>9.293163844140272</v>
       </c>
       <c r="E55">
-        <v>12.999</v>
+        <v>13.482</v>
       </c>
       <c r="F55">
-        <v>25.599</v>
+        <v>26.082</v>
       </c>
       <c r="G55">
         <v>17.5</v>
@@ -5791,28 +5791,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M55">
-        <v>6.036244200000001</v>
+        <v>6.150135600000001</v>
       </c>
       <c r="N55">
-        <v>-4.957577533333335</v>
+        <v>-5.071468933333334</v>
       </c>
       <c r="O55">
         <v>-0</v>
       </c>
       <c r="P55">
-        <v>-4.957577533333335</v>
+        <v>-5.071468933333334</v>
       </c>
       <c r="Q55">
-        <v>-4.944577533333335</v>
+        <v>-5.058468933333335</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1278569127169275</v>
+        <v>0.1296407586455563</v>
       </c>
       <c r="T55">
-        <v>1.599441961304239</v>
+        <v>1.634212438723896</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.1786983148671597</v>
+        <v>0.1753890868140642</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1869667489769559</v>
+        <v>0.1888667489769559</v>
       </c>
       <c r="C56">
-        <v>0.7111638441402697</v>
+        <v>0.1047458491824713</v>
       </c>
       <c r="D56">
-        <v>9.293163844140272</v>
+        <v>9.169745849182474</v>
       </c>
       <c r="E56">
-        <v>13.482</v>
+        <v>13.965</v>
       </c>
       <c r="F56">
-        <v>26.082</v>
+        <v>26.565</v>
       </c>
       <c r="G56">
         <v>17.5</v>
@@ -5873,28 +5873,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M56">
-        <v>6.150135600000001</v>
+        <v>6.264027000000001</v>
       </c>
       <c r="N56">
-        <v>-5.071468933333334</v>
+        <v>-5.185360333333334</v>
       </c>
       <c r="O56">
         <v>-0</v>
       </c>
       <c r="P56">
-        <v>-5.071468933333334</v>
+        <v>-5.185360333333334</v>
       </c>
       <c r="Q56">
-        <v>-5.058468933333335</v>
+        <v>-5.172360333333335</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1296407586455563</v>
+        <v>0.1315038866154576</v>
       </c>
       <c r="T56">
-        <v>1.634212438723896</v>
+        <v>1.670528270695538</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.1753890868140642</v>
+        <v>0.1722001943265358</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1888667489769559</v>
+        <v>0.1907667489769559</v>
       </c>
       <c r="C57">
-        <v>0.1047458491824713</v>
+        <v>-0.4984370012739241</v>
       </c>
       <c r="D57">
-        <v>9.169745849182474</v>
+        <v>9.049562998726083</v>
       </c>
       <c r="E57">
-        <v>13.965</v>
+        <v>14.448</v>
       </c>
       <c r="F57">
-        <v>26.565</v>
+        <v>27.04800000000001</v>
       </c>
       <c r="G57">
         <v>17.5</v>
@@ -5955,28 +5955,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M57">
-        <v>6.264027000000001</v>
+        <v>6.377918400000001</v>
       </c>
       <c r="N57">
-        <v>-5.185360333333334</v>
+        <v>-5.299251733333334</v>
       </c>
       <c r="O57">
         <v>-0</v>
       </c>
       <c r="P57">
-        <v>-5.185360333333334</v>
+        <v>-5.299251733333334</v>
       </c>
       <c r="Q57">
-        <v>-5.172360333333335</v>
+        <v>-5.286251733333335</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1315038866154576</v>
+        <v>0.1334517022203544</v>
       </c>
       <c r="T57">
-        <v>1.670528270695538</v>
+        <v>1.708494822302255</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.1722001943265358</v>
+        <v>0.169125190856419</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1907667489769559</v>
+        <v>0.1926667489769559</v>
       </c>
       <c r="C58">
-        <v>-0.4984370012739241</v>
+        <v>-1.098510265422213</v>
       </c>
       <c r="D58">
-        <v>9.049562998726083</v>
+        <v>8.932489734577793</v>
       </c>
       <c r="E58">
-        <v>14.448</v>
+        <v>14.931</v>
       </c>
       <c r="F58">
-        <v>27.04800000000001</v>
+        <v>27.53100000000001</v>
       </c>
       <c r="G58">
         <v>17.5</v>
@@ -6037,28 +6037,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M58">
-        <v>6.377918400000001</v>
+        <v>6.491809800000001</v>
       </c>
       <c r="N58">
-        <v>-5.299251733333334</v>
+        <v>-5.413143133333334</v>
       </c>
       <c r="O58">
         <v>-0</v>
       </c>
       <c r="P58">
-        <v>-5.299251733333334</v>
+        <v>-5.413143133333334</v>
       </c>
       <c r="Q58">
-        <v>-5.286251733333335</v>
+        <v>-5.400143133333335</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1334517022203544</v>
+        <v>0.1354901138998975</v>
       </c>
       <c r="T58">
-        <v>1.708494822302255</v>
+        <v>1.748227260030215</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.169125190856419</v>
+        <v>0.1661580822449029</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1926667489769559</v>
+        <v>0.1945667489769559</v>
       </c>
       <c r="C59">
-        <v>-1.098510265422213</v>
+        <v>-1.695593087103866</v>
       </c>
       <c r="D59">
-        <v>8.932489734577793</v>
+        <v>8.81840691289614</v>
       </c>
       <c r="E59">
-        <v>14.931</v>
+        <v>15.41400000000001</v>
       </c>
       <c r="F59">
-        <v>27.53100000000001</v>
+        <v>28.01400000000001</v>
       </c>
       <c r="G59">
         <v>17.5</v>
@@ -6119,28 +6119,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M59">
-        <v>6.491809800000001</v>
+        <v>6.605701200000002</v>
       </c>
       <c r="N59">
-        <v>-5.413143133333334</v>
+        <v>-5.527034533333335</v>
       </c>
       <c r="O59">
         <v>-0</v>
       </c>
       <c r="P59">
-        <v>-5.413143133333334</v>
+        <v>-5.527034533333335</v>
       </c>
       <c r="Q59">
-        <v>-5.400143133333335</v>
+        <v>-5.514034533333335</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1354901138998975</v>
+        <v>0.137625592802276</v>
       </c>
       <c r="T59">
-        <v>1.748227260030215</v>
+        <v>1.789851718602363</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1661580822449029</v>
+        <v>0.163293287723439</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1945667489769559</v>
+        <v>0.1964667489769559</v>
       </c>
       <c r="C60">
-        <v>-1.695593087103859</v>
+        <v>-2.28979860025305</v>
       </c>
       <c r="D60">
-        <v>8.81840691289614</v>
+        <v>8.707201399746948</v>
       </c>
       <c r="E60">
-        <v>15.414</v>
+        <v>15.897</v>
       </c>
       <c r="F60">
-        <v>28.014</v>
+        <v>28.497</v>
       </c>
       <c r="G60">
         <v>17.5</v>
@@ -6201,28 +6201,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M60">
-        <v>6.6057012</v>
+        <v>6.7195926</v>
       </c>
       <c r="N60">
-        <v>-5.527034533333333</v>
+        <v>-5.640925933333333</v>
       </c>
       <c r="O60">
         <v>-0</v>
       </c>
       <c r="P60">
-        <v>-5.527034533333333</v>
+        <v>-5.640925933333333</v>
       </c>
       <c r="Q60">
-        <v>-5.514034533333334</v>
+        <v>-5.627925933333334</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.137625592802276</v>
+        <v>0.1398652414072095</v>
       </c>
       <c r="T60">
-        <v>1.789851718602362</v>
+        <v>1.833506638568273</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1632932877234391</v>
+        <v>0.1605256048806689</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1964667489769559</v>
+        <v>0.1983667489769559</v>
       </c>
       <c r="C61">
-        <v>-2.28979860025305</v>
+        <v>-2.881234303120507</v>
       </c>
       <c r="D61">
-        <v>8.707201399746948</v>
+        <v>8.598765696879493</v>
       </c>
       <c r="E61">
-        <v>15.897</v>
+        <v>16.38</v>
       </c>
       <c r="F61">
-        <v>28.497</v>
+        <v>28.98</v>
       </c>
       <c r="G61">
         <v>17.5</v>
@@ -6283,28 +6283,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M61">
-        <v>6.7195926</v>
+        <v>6.833484</v>
       </c>
       <c r="N61">
-        <v>-5.640925933333333</v>
+        <v>-5.754817333333333</v>
       </c>
       <c r="O61">
         <v>-0</v>
       </c>
       <c r="P61">
-        <v>-5.640925933333333</v>
+        <v>-5.754817333333333</v>
       </c>
       <c r="Q61">
-        <v>-5.627925933333334</v>
+        <v>-5.741817333333334</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1398652414072095</v>
+        <v>0.1422168724423898</v>
       </c>
       <c r="T61">
-        <v>1.833506638568273</v>
+        <v>1.87934430453248</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1605256048806689</v>
+        <v>0.1578501781326578</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1983667489769559</v>
+        <v>0.2002667489769559</v>
       </c>
       <c r="C62">
-        <v>-2.881234303120507</v>
+        <v>-3.470002404878826</v>
       </c>
       <c r="D62">
-        <v>8.598765696879493</v>
+        <v>8.492997595121173</v>
       </c>
       <c r="E62">
-        <v>16.38</v>
+        <v>16.863</v>
       </c>
       <c r="F62">
-        <v>28.98</v>
+        <v>29.463</v>
       </c>
       <c r="G62">
         <v>17.5</v>
@@ -6365,28 +6365,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M62">
-        <v>6.833484</v>
+        <v>6.9473754</v>
       </c>
       <c r="N62">
-        <v>-5.754817333333333</v>
+        <v>-5.868708733333333</v>
       </c>
       <c r="O62">
         <v>-0</v>
       </c>
       <c r="P62">
-        <v>-5.754817333333333</v>
+        <v>-5.868708733333333</v>
       </c>
       <c r="Q62">
-        <v>-5.741817333333334</v>
+        <v>-5.855708733333334</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1422168724423898</v>
+        <v>0.1446890999409126</v>
       </c>
       <c r="T62">
-        <v>1.87934430453248</v>
+        <v>1.927532620033313</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1578501781326578</v>
+        <v>0.1552624702944175</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2002667489769559</v>
+        <v>0.2021667489769559</v>
       </c>
       <c r="C63">
-        <v>-3.470002404878826</v>
+        <v>-4.056200146958304</v>
       </c>
       <c r="D63">
-        <v>8.492997595121173</v>
+        <v>8.389799853041698</v>
       </c>
       <c r="E63">
-        <v>16.863</v>
+        <v>17.346</v>
       </c>
       <c r="F63">
-        <v>29.463</v>
+        <v>29.946</v>
       </c>
       <c r="G63">
         <v>17.5</v>
@@ -6447,28 +6447,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M63">
-        <v>6.9473754</v>
+        <v>7.0612668</v>
       </c>
       <c r="N63">
-        <v>-5.868708733333333</v>
+        <v>-5.982600133333333</v>
       </c>
       <c r="O63">
         <v>-0</v>
       </c>
       <c r="P63">
-        <v>-5.868708733333333</v>
+        <v>-5.982600133333333</v>
       </c>
       <c r="Q63">
-        <v>-5.855708733333334</v>
+        <v>-5.969600133333334</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1446890999409126</v>
+        <v>0.1472914446761998</v>
       </c>
       <c r="T63">
-        <v>1.927532620033313</v>
+        <v>1.978257162665769</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1552624702944175</v>
+        <v>0.1527582369025721</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2021667489769559</v>
+        <v>0.2040667489769559</v>
       </c>
       <c r="C64">
-        <v>-4.056200146958304</v>
+        <v>-4.639920101236889</v>
       </c>
       <c r="D64">
-        <v>8.389799853041698</v>
+        <v>8.289079898763113</v>
       </c>
       <c r="E64">
-        <v>17.346</v>
+        <v>17.829</v>
       </c>
       <c r="F64">
-        <v>29.946</v>
+        <v>30.429</v>
       </c>
       <c r="G64">
         <v>17.5</v>
@@ -6529,28 +6529,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M64">
-        <v>7.0612668</v>
+        <v>7.175158200000001</v>
       </c>
       <c r="N64">
-        <v>-5.982600133333333</v>
+        <v>-6.096491533333334</v>
       </c>
       <c r="O64">
         <v>-0</v>
       </c>
       <c r="P64">
-        <v>-5.982600133333333</v>
+        <v>-6.096491533333334</v>
       </c>
       <c r="Q64">
-        <v>-5.969600133333334</v>
+        <v>-6.083491533333334</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1472914446761998</v>
+        <v>0.1500344566944754</v>
       </c>
       <c r="T64">
-        <v>1.978257162665769</v>
+        <v>2.031723572467546</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1527582369025721</v>
+        <v>0.1503335029834836</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2040667489769559</v>
+        <v>0.2059667489769559</v>
       </c>
       <c r="C65">
-        <v>-4.639920101236889</v>
+        <v>-5.221250447006199</v>
       </c>
       <c r="D65">
-        <v>8.289079898763113</v>
+        <v>8.190749552993804</v>
       </c>
       <c r="E65">
-        <v>17.829</v>
+        <v>18.312</v>
       </c>
       <c r="F65">
-        <v>30.429</v>
+        <v>30.912</v>
       </c>
       <c r="G65">
         <v>17.5</v>
@@ -6611,28 +6611,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M65">
-        <v>7.175158200000001</v>
+        <v>7.289049600000001</v>
       </c>
       <c r="N65">
-        <v>-6.096491533333334</v>
+        <v>-6.210382933333334</v>
       </c>
       <c r="O65">
         <v>-0</v>
       </c>
       <c r="P65">
-        <v>-6.096491533333334</v>
+        <v>-6.210382933333334</v>
       </c>
       <c r="Q65">
-        <v>-6.083491533333334</v>
+        <v>-6.197382933333334</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1500344566944754</v>
+        <v>0.152929858269322</v>
       </c>
       <c r="T65">
-        <v>2.031723572467546</v>
+        <v>2.088160338369422</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1503335029834836</v>
+        <v>0.1479845419993666</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2059667489769559</v>
+        <v>0.2078667489769559</v>
       </c>
       <c r="C66">
-        <v>-5.221250447006199</v>
+        <v>-5.800275228455362</v>
       </c>
       <c r="D66">
-        <v>8.190749552993804</v>
+        <v>8.094724771544643</v>
       </c>
       <c r="E66">
-        <v>18.312</v>
+        <v>18.795</v>
       </c>
       <c r="F66">
-        <v>30.912</v>
+        <v>31.395</v>
       </c>
       <c r="G66">
         <v>17.5</v>
@@ -6693,28 +6693,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M66">
-        <v>7.289049600000001</v>
+        <v>7.402941000000001</v>
       </c>
       <c r="N66">
-        <v>-6.210382933333334</v>
+        <v>-6.324274333333334</v>
       </c>
       <c r="O66">
         <v>-0</v>
       </c>
       <c r="P66">
-        <v>-6.210382933333334</v>
+        <v>-6.324274333333334</v>
       </c>
       <c r="Q66">
-        <v>-6.197382933333334</v>
+        <v>-6.311274333333334</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.152929858269322</v>
+        <v>0.1559907113627312</v>
       </c>
       <c r="T66">
-        <v>2.088160338369422</v>
+        <v>2.147822062322835</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1479845419993666</v>
+        <v>0.1457078567378379</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2078667489769559</v>
+        <v>0.2097667489769559</v>
       </c>
       <c r="C67">
-        <v>-5.800275228455362</v>
+        <v>-6.377074594252971</v>
       </c>
       <c r="D67">
-        <v>8.094724771544643</v>
+        <v>8.000925405747033</v>
       </c>
       <c r="E67">
-        <v>18.795</v>
+        <v>19.278</v>
       </c>
       <c r="F67">
-        <v>31.395</v>
+        <v>31.878</v>
       </c>
       <c r="G67">
         <v>17.5</v>
@@ -6775,28 +6775,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M67">
-        <v>7.402941000000001</v>
+        <v>7.516832400000001</v>
       </c>
       <c r="N67">
-        <v>-6.324274333333334</v>
+        <v>-6.438165733333334</v>
       </c>
       <c r="O67">
         <v>-0</v>
       </c>
       <c r="P67">
-        <v>-6.324274333333334</v>
+        <v>-6.438165733333334</v>
       </c>
       <c r="Q67">
-        <v>-6.311274333333334</v>
+        <v>-6.425165733333334</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1559907113627312</v>
+        <v>0.1592316146381056</v>
       </c>
       <c r="T67">
-        <v>2.147822062322835</v>
+        <v>2.210993299449977</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1457078567378379</v>
+        <v>0.1435001619387798</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2097667489769559</v>
+        <v>0.2116667489769559</v>
       </c>
       <c r="C68">
-        <v>-6.377074594252971</v>
+        <v>-6.951725020662614</v>
       </c>
       <c r="D68">
-        <v>8.000925405747033</v>
+        <v>7.909274979337388</v>
       </c>
       <c r="E68">
-        <v>19.278</v>
+        <v>19.761</v>
       </c>
       <c r="F68">
-        <v>31.878</v>
+        <v>32.361</v>
       </c>
       <c r="G68">
         <v>17.5</v>
@@ -6857,28 +6857,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M68">
-        <v>7.516832400000001</v>
+        <v>7.630723800000001</v>
       </c>
       <c r="N68">
-        <v>-6.438165733333334</v>
+        <v>-6.552057133333334</v>
       </c>
       <c r="O68">
         <v>-0</v>
       </c>
       <c r="P68">
-        <v>-6.438165733333334</v>
+        <v>-6.552057133333334</v>
       </c>
       <c r="Q68">
-        <v>-6.425165733333334</v>
+        <v>-6.539057133333334</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1592316146381056</v>
+        <v>0.1626689362938058</v>
       </c>
       <c r="T68">
-        <v>2.210993299449977</v>
+        <v>2.277993096403007</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1435001619387798</v>
+        <v>0.141358368477007</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2116667489769559</v>
+        <v>0.2135667489769559</v>
       </c>
       <c r="C69">
-        <v>-6.951725020662614</v>
+        <v>-7.52429951949734</v>
       </c>
       <c r="D69">
-        <v>7.909274979337388</v>
+        <v>7.819700480502667</v>
       </c>
       <c r="E69">
-        <v>19.761</v>
+        <v>20.24400000000001</v>
       </c>
       <c r="F69">
-        <v>32.361</v>
+        <v>32.84400000000001</v>
       </c>
       <c r="G69">
         <v>17.5</v>
@@ -6939,28 +6939,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M69">
-        <v>7.630723800000001</v>
+        <v>7.744615200000002</v>
       </c>
       <c r="N69">
-        <v>-6.552057133333334</v>
+        <v>-6.665948533333335</v>
       </c>
       <c r="O69">
         <v>-0</v>
       </c>
       <c r="P69">
-        <v>-6.552057133333334</v>
+        <v>-6.665948533333335</v>
       </c>
       <c r="Q69">
-        <v>-6.539057133333334</v>
+        <v>-6.652948533333335</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1626689362938058</v>
+        <v>0.1663210905529872</v>
       </c>
       <c r="T69">
-        <v>2.277993096403007</v>
+        <v>2.349180380665601</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.141358368477007</v>
+        <v>0.1392795689405804</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2135667489769559</v>
+        <v>0.2154667489769559</v>
       </c>
       <c r="C70">
-        <v>-7.52429951949734</v>
+        <v>-8.094867832101553</v>
       </c>
       <c r="D70">
-        <v>7.819700480502667</v>
+        <v>7.732132167898453</v>
       </c>
       <c r="E70">
-        <v>20.24400000000001</v>
+        <v>20.727</v>
       </c>
       <c r="F70">
-        <v>32.84400000000001</v>
+        <v>33.32700000000001</v>
       </c>
       <c r="G70">
         <v>17.5</v>
@@ -7021,28 +7021,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M70">
-        <v>7.744615200000002</v>
+        <v>7.858506600000002</v>
       </c>
       <c r="N70">
-        <v>-6.665948533333335</v>
+        <v>-6.779839933333335</v>
       </c>
       <c r="O70">
         <v>-0</v>
       </c>
       <c r="P70">
-        <v>-6.665948533333335</v>
+        <v>-6.779839933333335</v>
       </c>
       <c r="Q70">
-        <v>-6.652948533333335</v>
+        <v>-6.766839933333335</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1663210905529872</v>
+        <v>0.1702088676675997</v>
       </c>
       <c r="T70">
-        <v>2.349180380665601</v>
+        <v>2.424960392945136</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1392795689405804</v>
+        <v>0.1372610244631807</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2154667489769559</v>
+        <v>0.2173667489769559</v>
       </c>
       <c r="C71">
-        <v>-8.094867832101553</v>
+        <v>-8.663496610443566</v>
       </c>
       <c r="D71">
-        <v>7.732132167898453</v>
+        <v>7.646503389556441</v>
       </c>
       <c r="E71">
-        <v>20.727</v>
+        <v>21.21000000000001</v>
       </c>
       <c r="F71">
-        <v>33.32700000000001</v>
+        <v>33.81000000000001</v>
       </c>
       <c r="G71">
         <v>17.5</v>
@@ -7103,28 +7103,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M71">
-        <v>7.858506600000002</v>
+        <v>7.972398000000003</v>
       </c>
       <c r="N71">
-        <v>-6.779839933333335</v>
+        <v>-6.893731333333336</v>
       </c>
       <c r="O71">
         <v>-0</v>
       </c>
       <c r="P71">
-        <v>-6.779839933333335</v>
+        <v>-6.893731333333336</v>
       </c>
       <c r="Q71">
-        <v>-6.766839933333335</v>
+        <v>-6.880731333333336</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1702088676675997</v>
+        <v>0.1743558299231864</v>
       </c>
       <c r="T71">
-        <v>2.424960392945136</v>
+        <v>2.505792406043307</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1372610244631807</v>
+        <v>0.1353001526851352</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2173667489769559</v>
+        <v>0.2192667489769559</v>
       </c>
       <c r="C72">
-        <v>-8.663496610443566</v>
+        <v>-9.230249586306897</v>
       </c>
       <c r="D72">
-        <v>7.646503389556441</v>
+        <v>7.562750413693111</v>
       </c>
       <c r="E72">
-        <v>21.21000000000001</v>
+        <v>21.693</v>
       </c>
       <c r="F72">
-        <v>33.81000000000001</v>
+        <v>34.29300000000001</v>
       </c>
       <c r="G72">
         <v>17.5</v>
@@ -7185,28 +7185,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M72">
-        <v>7.972398000000003</v>
+        <v>8.086289400000002</v>
       </c>
       <c r="N72">
-        <v>-6.893731333333336</v>
+        <v>-7.007622733333335</v>
       </c>
       <c r="O72">
         <v>-0</v>
       </c>
       <c r="P72">
-        <v>-6.893731333333336</v>
+        <v>-7.007622733333335</v>
       </c>
       <c r="Q72">
-        <v>-6.880731333333336</v>
+        <v>-6.994622733333335</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1743558299231864</v>
+        <v>0.1787887895757101</v>
       </c>
       <c r="T72">
-        <v>2.505792406043307</v>
+        <v>2.592199040734457</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1353001526851352</v>
+        <v>0.1333945167318235</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2192667489769559</v>
+        <v>0.2211667489769559</v>
       </c>
       <c r="C73">
-        <v>-9.23024958630689</v>
+        <v>-9.795187729483082</v>
       </c>
       <c r="D73">
-        <v>7.562750413693111</v>
+        <v>7.480812270516922</v>
       </c>
       <c r="E73">
-        <v>21.693</v>
+        <v>22.176</v>
       </c>
       <c r="F73">
-        <v>34.293</v>
+        <v>34.776</v>
       </c>
       <c r="G73">
         <v>17.5</v>
@@ -7267,28 +7267,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M73">
-        <v>8.0862894</v>
+        <v>8.200180800000002</v>
       </c>
       <c r="N73">
-        <v>-7.007622733333333</v>
+        <v>-7.121514133333335</v>
       </c>
       <c r="O73">
         <v>-0</v>
       </c>
       <c r="P73">
-        <v>-7.007622733333333</v>
+        <v>-7.121514133333335</v>
       </c>
       <c r="Q73">
-        <v>-6.994622733333333</v>
+        <v>-7.108514133333335</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.17878878957571</v>
+        <v>0.1835383892034139</v>
       </c>
       <c r="T73">
-        <v>2.592199040734455</v>
+        <v>2.684777577903543</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1333945167318235</v>
+        <v>0.1315418151105481</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2211667489769559</v>
+        <v>0.2230667489769559</v>
       </c>
       <c r="C74">
-        <v>-9.795187729483082</v>
+        <v>-10.35836939579112</v>
       </c>
       <c r="D74">
-        <v>7.480812270516922</v>
+        <v>7.400630604208878</v>
       </c>
       <c r="E74">
-        <v>22.176</v>
+        <v>22.659</v>
       </c>
       <c r="F74">
-        <v>34.776</v>
+        <v>35.259</v>
       </c>
       <c r="G74">
         <v>17.5</v>
@@ -7349,28 +7349,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M74">
-        <v>8.200180800000002</v>
+        <v>8.3140722</v>
       </c>
       <c r="N74">
-        <v>-7.121514133333335</v>
+        <v>-7.235405533333333</v>
       </c>
       <c r="O74">
         <v>-0</v>
       </c>
       <c r="P74">
-        <v>-7.121514133333335</v>
+        <v>-7.235405533333333</v>
       </c>
       <c r="Q74">
-        <v>-7.108514133333335</v>
+        <v>-7.222405533333333</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1835383892034139</v>
+        <v>0.1886398110257626</v>
       </c>
       <c r="T74">
-        <v>2.684777577903543</v>
+        <v>2.784213784492563</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1315418151105481</v>
+        <v>0.1297398724378009</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2230667489769559</v>
+        <v>0.2249667489769559</v>
       </c>
       <c r="C75">
-        <v>-10.35836939579112</v>
+        <v>-10.91985046567874</v>
       </c>
       <c r="D75">
-        <v>7.400630604208878</v>
+        <v>7.322149534321264</v>
       </c>
       <c r="E75">
-        <v>22.659</v>
+        <v>23.142</v>
       </c>
       <c r="F75">
-        <v>35.259</v>
+        <v>35.742</v>
       </c>
       <c r="G75">
         <v>17.5</v>
@@ -7431,28 +7431,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M75">
-        <v>8.3140722</v>
+        <v>8.427963600000002</v>
       </c>
       <c r="N75">
-        <v>-7.235405533333333</v>
+        <v>-7.349296933333335</v>
       </c>
       <c r="O75">
         <v>-0</v>
       </c>
       <c r="P75">
-        <v>-7.235405533333333</v>
+        <v>-7.349296933333335</v>
       </c>
       <c r="Q75">
-        <v>-7.222405533333333</v>
+        <v>-7.336296933333335</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1886398110257626</v>
+        <v>0.1941336499113689</v>
       </c>
       <c r="T75">
-        <v>2.784213784492563</v>
+        <v>2.891298930049969</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1297398724378009</v>
+        <v>0.1279866309183711</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2249667489769559</v>
+        <v>0.2268667489769559</v>
       </c>
       <c r="C76">
-        <v>-10.91985046567874</v>
+        <v>-11.47968447409726</v>
       </c>
       <c r="D76">
-        <v>7.322149534321264</v>
+        <v>7.24531552590274</v>
       </c>
       <c r="E76">
-        <v>23.142</v>
+        <v>23.625</v>
       </c>
       <c r="F76">
-        <v>35.742</v>
+        <v>36.225</v>
       </c>
       <c r="G76">
         <v>17.5</v>
@@ -7513,28 +7513,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M76">
-        <v>8.427963600000002</v>
+        <v>8.541855</v>
       </c>
       <c r="N76">
-        <v>-7.349296933333335</v>
+        <v>-7.463188333333333</v>
       </c>
       <c r="O76">
         <v>-0</v>
       </c>
       <c r="P76">
-        <v>-7.349296933333335</v>
+        <v>-7.463188333333333</v>
       </c>
       <c r="Q76">
-        <v>-7.336296933333335</v>
+        <v>-7.450188333333333</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1941336499113689</v>
+        <v>0.2000669959078236</v>
       </c>
       <c r="T76">
-        <v>2.891298930049969</v>
+        <v>3.006950887251969</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1279866309183711</v>
+        <v>0.1262801425061262</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2268667489769559</v>
+        <v>0.2287667489769559</v>
       </c>
       <c r="C77">
-        <v>-11.47968447409726</v>
+        <v>-12.03792273228454</v>
       </c>
       <c r="D77">
-        <v>7.24531552590274</v>
+        <v>7.170077267715461</v>
       </c>
       <c r="E77">
-        <v>23.625</v>
+        <v>24.108</v>
       </c>
       <c r="F77">
-        <v>36.225</v>
+        <v>36.70800000000001</v>
       </c>
       <c r="G77">
         <v>17.5</v>
@@ -7595,28 +7595,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M77">
-        <v>8.541855</v>
+        <v>8.655746400000002</v>
       </c>
       <c r="N77">
-        <v>-7.463188333333333</v>
+        <v>-7.577079733333335</v>
       </c>
       <c r="O77">
         <v>-0</v>
       </c>
       <c r="P77">
-        <v>-7.463188333333333</v>
+        <v>-7.577079733333335</v>
       </c>
       <c r="Q77">
-        <v>-7.450188333333333</v>
+        <v>-7.564079733333335</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2000669959078236</v>
+        <v>0.206494787403983</v>
       </c>
       <c r="T77">
-        <v>3.006950887251969</v>
+        <v>3.132240507554134</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1262801425061262</v>
+        <v>0.1246185616836771</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2287667489769559</v>
+        <v>0.2306667489769559</v>
       </c>
       <c r="C78">
-        <v>-12.03792273228454</v>
+        <v>-12.59461444203792</v>
       </c>
       <c r="D78">
-        <v>7.170077267715461</v>
+        <v>7.096385557962087</v>
       </c>
       <c r="E78">
-        <v>24.108</v>
+        <v>24.591</v>
       </c>
       <c r="F78">
-        <v>36.70800000000001</v>
+        <v>37.191</v>
       </c>
       <c r="G78">
         <v>17.5</v>
@@ -7677,28 +7677,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M78">
-        <v>8.655746400000002</v>
+        <v>8.769637800000002</v>
       </c>
       <c r="N78">
-        <v>-7.577079733333335</v>
+        <v>-7.690971133333335</v>
       </c>
       <c r="O78">
         <v>-0</v>
       </c>
       <c r="P78">
-        <v>-7.577079733333335</v>
+        <v>-7.690971133333335</v>
       </c>
       <c r="Q78">
-        <v>-7.564079733333335</v>
+        <v>-7.677971133333335</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.206494787403983</v>
+        <v>0.2134815172911126</v>
       </c>
       <c r="T78">
-        <v>3.132240507554134</v>
+        <v>3.268424877447792</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1246185616836771</v>
+        <v>0.1230001388046684</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2306667489769559</v>
+        <v>0.2325667489769559</v>
       </c>
       <c r="C79">
-        <v>-12.59461444203792</v>
+        <v>-13.14980680301215</v>
       </c>
       <c r="D79">
-        <v>7.096385557962087</v>
+        <v>7.024193196987857</v>
       </c>
       <c r="E79">
-        <v>24.591</v>
+        <v>25.07400000000001</v>
       </c>
       <c r="F79">
-        <v>37.191</v>
+        <v>37.67400000000001</v>
       </c>
       <c r="G79">
         <v>17.5</v>
@@ -7759,28 +7759,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M79">
-        <v>8.769637800000002</v>
+        <v>8.883529200000002</v>
       </c>
       <c r="N79">
-        <v>-7.690971133333335</v>
+        <v>-7.804862533333335</v>
       </c>
       <c r="O79">
         <v>-0</v>
       </c>
       <c r="P79">
-        <v>-7.690971133333335</v>
+        <v>-7.804862533333335</v>
       </c>
       <c r="Q79">
-        <v>-7.677971133333335</v>
+        <v>-7.791862533333335</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2134815172911126</v>
+        <v>0.2211034044407087</v>
       </c>
       <c r="T79">
-        <v>3.268424877447792</v>
+        <v>3.41698964460451</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1230001388046684</v>
+        <v>0.1214232139481983</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2325667489769559</v>
+        <v>0.2344667489769559</v>
       </c>
       <c r="C80">
-        <v>-13.14980680301215</v>
+        <v>-13.70354511353398</v>
       </c>
       <c r="D80">
-        <v>7.024193196987857</v>
+        <v>6.953454886466022</v>
       </c>
       <c r="E80">
-        <v>25.07400000000001</v>
+        <v>25.557</v>
       </c>
       <c r="F80">
-        <v>37.67400000000001</v>
+        <v>38.157</v>
       </c>
       <c r="G80">
         <v>17.5</v>
@@ -7841,28 +7841,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M80">
-        <v>8.883529200000002</v>
+        <v>8.997420600000002</v>
       </c>
       <c r="N80">
-        <v>-7.804862533333335</v>
+        <v>-7.918753933333335</v>
       </c>
       <c r="O80">
         <v>-0</v>
       </c>
       <c r="P80">
-        <v>-7.804862533333335</v>
+        <v>-7.918753933333335</v>
       </c>
       <c r="Q80">
-        <v>-7.791862533333335</v>
+        <v>-7.905753933333335</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2211034044407087</v>
+        <v>0.229451185604552</v>
       </c>
       <c r="T80">
-        <v>3.41698964460451</v>
+        <v>3.579703437204725</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1214232139481983</v>
+        <v>0.1198862112399932</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2344667489769559</v>
+        <v>0.2363667489769559</v>
       </c>
       <c r="C81">
-        <v>-13.70354511353398</v>
+        <v>-14.25587286538582</v>
       </c>
       <c r="D81">
-        <v>6.953454886466022</v>
+        <v>6.884127134614188</v>
       </c>
       <c r="E81">
-        <v>25.557</v>
+        <v>26.04000000000001</v>
       </c>
       <c r="F81">
-        <v>38.157</v>
+        <v>38.64000000000001</v>
       </c>
       <c r="G81">
         <v>17.5</v>
@@ -7923,28 +7923,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M81">
-        <v>8.997420600000002</v>
+        <v>9.111312000000002</v>
       </c>
       <c r="N81">
-        <v>-7.918753933333335</v>
+        <v>-8.032645333333335</v>
       </c>
       <c r="O81">
         <v>-0</v>
       </c>
       <c r="P81">
-        <v>-7.918753933333335</v>
+        <v>-8.032645333333335</v>
       </c>
       <c r="Q81">
-        <v>-7.905753933333335</v>
+        <v>-8.019645333333335</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.229451185604552</v>
+        <v>0.2386337448847796</v>
       </c>
       <c r="T81">
-        <v>3.579703437204725</v>
+        <v>3.758688609064961</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1198862112399932</v>
+        <v>0.1183876335994933</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2363667489769559</v>
+        <v>0.2382667489769559</v>
       </c>
       <c r="C82">
-        <v>-14.25587286538582</v>
+        <v>-14.80683183297524</v>
       </c>
       <c r="D82">
-        <v>6.884127134614188</v>
+        <v>6.816168167024761</v>
       </c>
       <c r="E82">
-        <v>26.04000000000001</v>
+        <v>26.523</v>
       </c>
       <c r="F82">
-        <v>38.64000000000001</v>
+        <v>39.123</v>
       </c>
       <c r="G82">
         <v>17.5</v>
@@ -8005,28 +8005,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M82">
-        <v>9.111312000000002</v>
+        <v>9.225203400000002</v>
       </c>
       <c r="N82">
-        <v>-8.032645333333335</v>
+        <v>-8.146536733333335</v>
       </c>
       <c r="O82">
         <v>-0</v>
       </c>
       <c r="P82">
-        <v>-8.032645333333335</v>
+        <v>-8.146536733333335</v>
       </c>
       <c r="Q82">
-        <v>-8.019645333333335</v>
+        <v>-8.133536733333335</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2386337448847796</v>
+        <v>0.2487828893523996</v>
       </c>
       <c r="T82">
-        <v>3.758688609064961</v>
+        <v>3.956514325331538</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1183876335994933</v>
+        <v>0.1169260578760428</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2382667489769559</v>
+        <v>0.2401667489769559</v>
       </c>
       <c r="C83">
-        <v>-14.80683183297524</v>
+        <v>-15.35646215727461</v>
       </c>
       <c r="D83">
-        <v>6.816168167024761</v>
+        <v>6.749537842725401</v>
       </c>
       <c r="E83">
-        <v>26.523</v>
+        <v>27.00600000000001</v>
       </c>
       <c r="F83">
-        <v>39.123</v>
+        <v>39.60600000000001</v>
       </c>
       <c r="G83">
         <v>17.5</v>
@@ -8087,28 +8087,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M83">
-        <v>9.225203400000002</v>
+        <v>9.339094800000002</v>
       </c>
       <c r="N83">
-        <v>-8.146536733333335</v>
+        <v>-8.260428133333335</v>
       </c>
       <c r="O83">
         <v>-0</v>
       </c>
       <c r="P83">
-        <v>-8.146536733333335</v>
+        <v>-8.260428133333335</v>
       </c>
       <c r="Q83">
-        <v>-8.133536733333335</v>
+        <v>-8.247428133333335</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2487828893523996</v>
+        <v>0.260059716538644</v>
       </c>
       <c r="T83">
-        <v>3.956514325331538</v>
+        <v>4.176320676738847</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1169260578760428</v>
+        <v>0.1155001303409691</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2401667489769559</v>
+        <v>0.2420667489769559</v>
       </c>
       <c r="C84">
-        <v>-15.35646215727461</v>
+        <v>-15.90480242488501</v>
       </c>
       <c r="D84">
-        <v>6.749537842725401</v>
+        <v>6.684197575114996</v>
       </c>
       <c r="E84">
-        <v>27.00600000000001</v>
+        <v>27.489</v>
       </c>
       <c r="F84">
-        <v>39.60600000000001</v>
+        <v>40.08900000000001</v>
       </c>
       <c r="G84">
         <v>17.5</v>
@@ -8169,28 +8169,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M84">
-        <v>9.339094800000002</v>
+        <v>9.452986200000002</v>
       </c>
       <c r="N84">
-        <v>-8.260428133333335</v>
+        <v>-8.374319533333335</v>
       </c>
       <c r="O84">
         <v>-0</v>
       </c>
       <c r="P84">
-        <v>-8.260428133333335</v>
+        <v>-8.374319533333335</v>
       </c>
       <c r="Q84">
-        <v>-8.247428133333335</v>
+        <v>-8.361319533333335</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.260059716538644</v>
+        <v>0.2726632292762113</v>
       </c>
       <c r="T84">
-        <v>4.176320676738847</v>
+        <v>4.421986598899956</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1155001303409691</v>
+        <v>0.1141085625055357</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2420667489769559</v>
+        <v>0.2439667489769559</v>
       </c>
       <c r="C85">
-        <v>-15.90480242488501</v>
+        <v>-16.45188974255199</v>
       </c>
       <c r="D85">
-        <v>6.684197575114996</v>
+        <v>6.620110257448019</v>
       </c>
       <c r="E85">
-        <v>27.489</v>
+        <v>27.97200000000001</v>
       </c>
       <c r="F85">
-        <v>40.08900000000001</v>
+        <v>40.57200000000001</v>
       </c>
       <c r="G85">
         <v>17.5</v>
@@ -8251,28 +8251,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M85">
-        <v>9.452986200000002</v>
+        <v>9.566877600000003</v>
       </c>
       <c r="N85">
-        <v>-8.374319533333335</v>
+        <v>-8.488210933333336</v>
       </c>
       <c r="O85">
         <v>-0</v>
       </c>
       <c r="P85">
-        <v>-8.374319533333335</v>
+        <v>-8.488210933333336</v>
       </c>
       <c r="Q85">
-        <v>-8.361319533333335</v>
+        <v>-8.475210933333337</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2726632292762113</v>
+        <v>0.2868421811059745</v>
       </c>
       <c r="T85">
-        <v>4.421986598899956</v>
+        <v>4.698360761331204</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1141085625055357</v>
+        <v>0.1127501272376127</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2439667489769559</v>
+        <v>0.2458667489769559</v>
       </c>
       <c r="C86">
-        <v>-16.45188974255198</v>
+        <v>-16.99775980743517</v>
       </c>
       <c r="D86">
-        <v>6.620110257448019</v>
+        <v>6.557240192564825</v>
       </c>
       <c r="E86">
-        <v>27.972</v>
+        <v>28.455</v>
       </c>
       <c r="F86">
-        <v>40.572</v>
+        <v>41.055</v>
       </c>
       <c r="G86">
         <v>17.5</v>
@@ -8333,28 +8333,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M86">
-        <v>9.566877600000002</v>
+        <v>9.680769</v>
       </c>
       <c r="N86">
-        <v>-8.488210933333335</v>
+        <v>-8.602102333333333</v>
       </c>
       <c r="O86">
         <v>-0</v>
       </c>
       <c r="P86">
-        <v>-8.488210933333335</v>
+        <v>-8.602102333333333</v>
       </c>
       <c r="Q86">
-        <v>-8.475210933333335</v>
+        <v>-8.589102333333333</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2868421811059744</v>
+        <v>0.3029116598463727</v>
       </c>
       <c r="T86">
-        <v>4.6983607613312</v>
+        <v>5.011584812086614</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1127501272376127</v>
+        <v>0.1114236551524643</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2458667489769559</v>
+        <v>0.2477667489769559</v>
       </c>
       <c r="C87">
-        <v>-16.99775980743517</v>
+        <v>-17.54244697341167</v>
       </c>
       <c r="D87">
-        <v>6.557240192564825</v>
+        <v>6.495553026588337</v>
       </c>
       <c r="E87">
-        <v>28.455</v>
+        <v>28.938</v>
       </c>
       <c r="F87">
-        <v>41.055</v>
+        <v>41.538</v>
       </c>
       <c r="G87">
         <v>17.5</v>
@@ -8415,28 +8415,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M87">
-        <v>9.680769</v>
+        <v>9.794660400000001</v>
       </c>
       <c r="N87">
-        <v>-8.602102333333333</v>
+        <v>-8.715993733333335</v>
       </c>
       <c r="O87">
         <v>-0</v>
       </c>
       <c r="P87">
-        <v>-8.602102333333333</v>
+        <v>-8.715993733333335</v>
       </c>
       <c r="Q87">
-        <v>-8.589102333333333</v>
+        <v>-8.702993733333335</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3029116598463727</v>
+        <v>0.3212767784068279</v>
       </c>
       <c r="T87">
-        <v>5.011584812086614</v>
+        <v>5.369555155807086</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1114236551524643</v>
+        <v>0.1101280312553427</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2477667489769559</v>
+        <v>0.2496667489769559</v>
       </c>
       <c r="C88">
-        <v>-17.54244697341167</v>
+        <v>-18.08598431367166</v>
       </c>
       <c r="D88">
-        <v>6.495553026588337</v>
+        <v>6.435015686328337</v>
       </c>
       <c r="E88">
-        <v>28.938</v>
+        <v>29.421</v>
       </c>
       <c r="F88">
-        <v>41.538</v>
+        <v>42.021</v>
       </c>
       <c r="G88">
         <v>17.5</v>
@@ -8497,28 +8497,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M88">
-        <v>9.794660400000001</v>
+        <v>9.908551800000001</v>
       </c>
       <c r="N88">
-        <v>-8.715993733333335</v>
+        <v>-8.829885133333335</v>
       </c>
       <c r="O88">
         <v>-0</v>
       </c>
       <c r="P88">
-        <v>-8.715993733333335</v>
+        <v>-8.829885133333335</v>
       </c>
       <c r="Q88">
-        <v>-8.702993733333335</v>
+        <v>-8.816885133333335</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3212767784068279</v>
+        <v>0.3424672998227377</v>
       </c>
       <c r="T88">
-        <v>5.369555155807086</v>
+        <v>5.782597860099939</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1101280312553427</v>
+        <v>0.1088621918156261</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2496667489769559</v>
+        <v>0.2515667489769559</v>
       </c>
       <c r="C89">
-        <v>-18.08598431367166</v>
+        <v>-18.62840367984629</v>
       </c>
       <c r="D89">
-        <v>6.435015686328337</v>
+        <v>6.375596320153712</v>
       </c>
       <c r="E89">
-        <v>29.421</v>
+        <v>29.904</v>
       </c>
       <c r="F89">
-        <v>42.021</v>
+        <v>42.504</v>
       </c>
       <c r="G89">
         <v>17.5</v>
@@ -8579,28 +8579,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M89">
-        <v>9.908551800000001</v>
+        <v>10.0224432</v>
       </c>
       <c r="N89">
-        <v>-8.829885133333335</v>
+        <v>-8.943776533333335</v>
       </c>
       <c r="O89">
         <v>-0</v>
       </c>
       <c r="P89">
-        <v>-8.829885133333335</v>
+        <v>-8.943776533333335</v>
       </c>
       <c r="Q89">
-        <v>-8.816885133333335</v>
+        <v>-8.930776533333335</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3424672998227377</v>
+        <v>0.3671895748079659</v>
       </c>
       <c r="T89">
-        <v>5.782597860099939</v>
+        <v>6.264481015108268</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1088621918156261</v>
+        <v>0.1076251214540849</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2515667489769559</v>
+        <v>0.2534667489769559</v>
       </c>
       <c r="C90">
-        <v>-18.62840367984629</v>
+        <v>-19.16973575788944</v>
       </c>
       <c r="D90">
-        <v>6.375596320153712</v>
+        <v>6.317264242110557</v>
       </c>
       <c r="E90">
-        <v>29.904</v>
+        <v>30.387</v>
       </c>
       <c r="F90">
-        <v>42.504</v>
+        <v>42.987</v>
       </c>
       <c r="G90">
         <v>17.5</v>
@@ -8661,28 +8661,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M90">
-        <v>10.0224432</v>
+        <v>10.1363346</v>
       </c>
       <c r="N90">
-        <v>-8.943776533333335</v>
+        <v>-9.057667933333335</v>
       </c>
       <c r="O90">
         <v>-0</v>
       </c>
       <c r="P90">
-        <v>-8.943776533333335</v>
+        <v>-9.057667933333335</v>
       </c>
       <c r="Q90">
-        <v>-8.930776533333335</v>
+        <v>-9.044667933333335</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3671895748079659</v>
+        <v>0.3964068088814174</v>
       </c>
       <c r="T90">
-        <v>6.264481015108268</v>
+        <v>6.833979289209021</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1076251214540849</v>
+        <v>0.1064158504265108</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2534667489769559</v>
+        <v>0.2553667489769559</v>
       </c>
       <c r="C91">
-        <v>-19.16973575788944</v>
+        <v>-19.71001012091987</v>
       </c>
       <c r="D91">
-        <v>6.317264242110557</v>
+        <v>6.259989879080139</v>
       </c>
       <c r="E91">
-        <v>30.387</v>
+        <v>30.87</v>
       </c>
       <c r="F91">
-        <v>42.987</v>
+        <v>43.47000000000001</v>
       </c>
       <c r="G91">
         <v>17.5</v>
@@ -8743,28 +8743,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M91">
-        <v>10.1363346</v>
+        <v>10.250226</v>
       </c>
       <c r="N91">
-        <v>-9.057667933333335</v>
+        <v>-9.171559333333335</v>
       </c>
       <c r="O91">
         <v>-0</v>
       </c>
       <c r="P91">
-        <v>-9.057667933333335</v>
+        <v>-9.171559333333335</v>
       </c>
       <c r="Q91">
-        <v>-9.044667933333335</v>
+        <v>-9.158559333333335</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3964068088814174</v>
+        <v>0.4314674897695592</v>
       </c>
       <c r="T91">
-        <v>6.833979289209021</v>
+        <v>7.517377218129923</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1064158504265108</v>
+        <v>0.1052334520884385</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2553667489769559</v>
+        <v>0.257266748976956</v>
       </c>
       <c r="C92">
-        <v>-19.71001012091987</v>
+        <v>-20.24925527921446</v>
       </c>
       <c r="D92">
-        <v>6.259989879080139</v>
+        <v>6.203744720785545</v>
       </c>
       <c r="E92">
-        <v>30.87</v>
+        <v>31.353</v>
       </c>
       <c r="F92">
-        <v>43.47000000000001</v>
+        <v>43.953</v>
       </c>
       <c r="G92">
         <v>17.5</v>
@@ -8825,28 +8825,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M92">
-        <v>10.250226</v>
+        <v>10.3641174</v>
       </c>
       <c r="N92">
-        <v>-9.171559333333335</v>
+        <v>-9.285450733333334</v>
       </c>
       <c r="O92">
         <v>-0</v>
       </c>
       <c r="P92">
-        <v>-9.171559333333335</v>
+        <v>-9.285450733333334</v>
       </c>
       <c r="Q92">
-        <v>-9.158559333333335</v>
+        <v>-9.272450733333335</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4314674897695592</v>
+        <v>0.474319433077288</v>
       </c>
       <c r="T92">
-        <v>7.517377218129923</v>
+        <v>8.352641353477694</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1052334520884385</v>
+        <v>0.1040770405270272</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.257266748976956</v>
+        <v>0.2591667489769559</v>
       </c>
       <c r="C93">
-        <v>-20.24925527921446</v>
+        <v>-20.78749872753061</v>
       </c>
       <c r="D93">
-        <v>6.203744720785545</v>
+        <v>6.148501272469399</v>
       </c>
       <c r="E93">
-        <v>31.353</v>
+        <v>31.83600000000001</v>
       </c>
       <c r="F93">
-        <v>43.953</v>
+        <v>44.43600000000001</v>
       </c>
       <c r="G93">
         <v>17.5</v>
@@ -8907,28 +8907,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M93">
-        <v>10.3641174</v>
+        <v>10.4780088</v>
       </c>
       <c r="N93">
-        <v>-9.285450733333334</v>
+        <v>-9.399342133333334</v>
       </c>
       <c r="O93">
         <v>-0</v>
       </c>
       <c r="P93">
-        <v>-9.285450733333334</v>
+        <v>-9.399342133333334</v>
       </c>
       <c r="Q93">
-        <v>-9.272450733333335</v>
+        <v>-9.386342133333335</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.474319433077288</v>
+        <v>0.5278843622119491</v>
       </c>
       <c r="T93">
-        <v>8.352641353477694</v>
+        <v>9.396721522662407</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1040770405270272</v>
+        <v>0.1029457683473854</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2591667489769559</v>
+        <v>0.2610667489769559</v>
       </c>
       <c r="C94">
-        <v>-20.78749872753061</v>
+        <v>-21.32476698992231</v>
       </c>
       <c r="D94">
-        <v>6.148501272469399</v>
+        <v>6.09423301007769</v>
       </c>
       <c r="E94">
-        <v>31.83600000000001</v>
+        <v>32.319</v>
       </c>
       <c r="F94">
-        <v>44.43600000000001</v>
+        <v>44.919</v>
       </c>
       <c r="G94">
         <v>17.5</v>
@@ -8989,28 +8989,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M94">
-        <v>10.4780088</v>
+        <v>10.5919002</v>
       </c>
       <c r="N94">
-        <v>-9.399342133333334</v>
+        <v>-9.513233533333334</v>
       </c>
       <c r="O94">
         <v>-0</v>
       </c>
       <c r="P94">
-        <v>-9.399342133333334</v>
+        <v>-9.513233533333334</v>
       </c>
       <c r="Q94">
-        <v>-9.386342133333335</v>
+        <v>-9.500233533333335</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5278843622119491</v>
+        <v>0.5967535568136562</v>
       </c>
       <c r="T94">
-        <v>9.396721522662407</v>
+        <v>10.73911031161418</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1029457683473854</v>
+        <v>0.1018388246017147</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2610667489769559</v>
+        <v>0.2629667489769559</v>
       </c>
       <c r="C95">
-        <v>-21.32476698992231</v>
+        <v>-21.86108566220385</v>
       </c>
       <c r="D95">
-        <v>6.09423301007769</v>
+        <v>6.040914337796161</v>
       </c>
       <c r="E95">
-        <v>32.319</v>
+        <v>32.80200000000001</v>
       </c>
       <c r="F95">
-        <v>44.919</v>
+        <v>45.40200000000001</v>
       </c>
       <c r="G95">
         <v>17.5</v>
@@ -9071,28 +9071,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M95">
-        <v>10.5919002</v>
+        <v>10.7057916</v>
       </c>
       <c r="N95">
-        <v>-9.513233533333334</v>
+        <v>-9.627124933333336</v>
       </c>
       <c r="O95">
         <v>-0</v>
       </c>
       <c r="P95">
-        <v>-9.513233533333334</v>
+        <v>-9.627124933333336</v>
       </c>
       <c r="Q95">
-        <v>-9.500233533333335</v>
+        <v>-9.614124933333336</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5967535568136562</v>
+        <v>0.6885791496159324</v>
       </c>
       <c r="T95">
-        <v>10.73911031161418</v>
+        <v>12.52896203021655</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1018388246017147</v>
+        <v>0.1007554328506326</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2629667489769559</v>
+        <v>0.2648667489769559</v>
       </c>
       <c r="C96">
-        <v>-21.86108566220385</v>
+        <v>-22.39647945220353</v>
       </c>
       <c r="D96">
-        <v>6.040914337796161</v>
+        <v>5.988520547796472</v>
       </c>
       <c r="E96">
-        <v>32.80200000000001</v>
+        <v>33.285</v>
       </c>
       <c r="F96">
-        <v>45.40200000000001</v>
+        <v>45.88500000000001</v>
       </c>
       <c r="G96">
         <v>17.5</v>
@@ -9153,28 +9153,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M96">
-        <v>10.7057916</v>
+        <v>10.819683</v>
       </c>
       <c r="N96">
-        <v>-9.627124933333336</v>
+        <v>-9.741016333333334</v>
       </c>
       <c r="O96">
         <v>-0</v>
       </c>
       <c r="P96">
-        <v>-9.627124933333336</v>
+        <v>-9.741016333333334</v>
       </c>
       <c r="Q96">
-        <v>-9.614124933333336</v>
+        <v>-9.728016333333334</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6885791496159324</v>
+        <v>0.8171349795391193</v>
       </c>
       <c r="T96">
-        <v>12.52896203021655</v>
+        <v>15.03475443625987</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1007554328506326</v>
+        <v>0.09969484934694173</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2648667489769559</v>
+        <v>0.2667667489769559</v>
       </c>
       <c r="C97">
-        <v>-22.39647945220353</v>
+        <v>-22.93097221794088</v>
       </c>
       <c r="D97">
-        <v>5.988520547796472</v>
+        <v>5.937027782059127</v>
       </c>
       <c r="E97">
-        <v>33.285</v>
+        <v>33.76800000000001</v>
       </c>
       <c r="F97">
-        <v>45.88500000000001</v>
+        <v>46.36800000000001</v>
       </c>
       <c r="G97">
         <v>17.5</v>
@@ -9235,28 +9235,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M97">
-        <v>10.819683</v>
+        <v>10.9335744</v>
       </c>
       <c r="N97">
-        <v>-9.741016333333334</v>
+        <v>-9.854907733333336</v>
       </c>
       <c r="O97">
         <v>-0</v>
       </c>
       <c r="P97">
-        <v>-9.741016333333334</v>
+        <v>-9.854907733333336</v>
       </c>
       <c r="Q97">
-        <v>-9.728016333333334</v>
+        <v>-9.841907733333336</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8171349795391193</v>
+        <v>1.0099687244239</v>
       </c>
       <c r="T97">
-        <v>15.03475443625987</v>
+        <v>18.79344304532484</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.09969484934694173</v>
+        <v>0.09865636133291111</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.266766748976956</v>
+        <v>0.2686667489769559</v>
       </c>
       <c r="C98">
-        <v>-22.93097221794088</v>
+        <v>-23.46458700385082</v>
       </c>
       <c r="D98">
-        <v>5.937027782059127</v>
+        <v>5.88641299614919</v>
       </c>
       <c r="E98">
-        <v>33.768</v>
+        <v>34.251</v>
       </c>
       <c r="F98">
-        <v>46.368</v>
+        <v>46.85100000000001</v>
       </c>
       <c r="G98">
         <v>17.5</v>
@@ -9317,28 +9317,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M98">
-        <v>10.9335744</v>
+        <v>11.0474658</v>
       </c>
       <c r="N98">
-        <v>-9.854907733333334</v>
+        <v>-9.968799133333334</v>
       </c>
       <c r="O98">
         <v>-0</v>
       </c>
       <c r="P98">
-        <v>-9.854907733333334</v>
+        <v>-9.968799133333334</v>
       </c>
       <c r="Q98">
-        <v>-9.841907733333334</v>
+        <v>-9.955799133333334</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.009968724423897</v>
+        <v>1.331358299231863</v>
       </c>
       <c r="T98">
-        <v>18.79344304532479</v>
+        <v>25.05792406043305</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.09865636133291111</v>
+        <v>0.09763928544288114</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2686667489769559</v>
+        <v>0.2705667489769559</v>
       </c>
       <c r="C99">
-        <v>-23.46458700385082</v>
+        <v>-23.9973460751707</v>
       </c>
       <c r="D99">
-        <v>5.88641299614919</v>
+        <v>5.836653924829303</v>
       </c>
       <c r="E99">
-        <v>34.251</v>
+        <v>34.734</v>
       </c>
       <c r="F99">
-        <v>46.85100000000001</v>
+        <v>47.334</v>
       </c>
       <c r="G99">
         <v>17.5</v>
@@ -9399,28 +9399,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M99">
-        <v>11.0474658</v>
+        <v>11.1613572</v>
       </c>
       <c r="N99">
-        <v>-9.968799133333334</v>
+        <v>-10.08269053333333</v>
       </c>
       <c r="O99">
         <v>-0</v>
       </c>
       <c r="P99">
-        <v>-9.968799133333334</v>
+        <v>-10.08269053333333</v>
       </c>
       <c r="Q99">
-        <v>-9.955799133333334</v>
+        <v>-10.06969053333333</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.331358299231863</v>
+        <v>1.974137448847794</v>
       </c>
       <c r="T99">
-        <v>25.05792406043305</v>
+        <v>37.58688609064958</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.09763928544288114</v>
+        <v>0.09664296620366808</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2705667489769559</v>
+        <v>0.2724667489769559</v>
       </c>
       <c r="C100">
-        <v>-23.9973460751707</v>
+        <v>-24.52927095059786</v>
       </c>
       <c r="D100">
-        <v>5.836653924829303</v>
+        <v>5.787729049402147</v>
       </c>
       <c r="E100">
-        <v>34.734</v>
+        <v>35.21700000000001</v>
       </c>
       <c r="F100">
-        <v>47.334</v>
+        <v>47.81700000000001</v>
       </c>
       <c r="G100">
         <v>17.5</v>
@@ -9481,28 +9481,28 @@
         <v>1.078666666666667</v>
       </c>
       <c r="M100">
-        <v>11.1613572</v>
+        <v>11.2752486</v>
       </c>
       <c r="N100">
-        <v>-10.08269053333333</v>
+        <v>-10.19658193333334</v>
       </c>
       <c r="O100">
         <v>-0</v>
       </c>
       <c r="P100">
-        <v>-10.08269053333333</v>
+        <v>-10.19658193333334</v>
       </c>
       <c r="Q100">
-        <v>-10.06969053333333</v>
+        <v>-10.18358193333334</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.974137448847794</v>
+        <v>3.902474897695588</v>
       </c>
       <c r="T100">
-        <v>37.58688609064958</v>
+        <v>75.17377218129916</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.09664296620366808</v>
+        <v>0.09566677462585316</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2724667489769559</v>
-      </c>
-      <c r="C101">
-        <v>-24.52927095059786</v>
-      </c>
-      <c r="D101">
-        <v>5.787729049402147</v>
-      </c>
-      <c r="E101">
-        <v>35.21700000000001</v>
-      </c>
-      <c r="F101">
-        <v>47.81700000000001</v>
-      </c>
-      <c r="G101">
-        <v>17.5</v>
-      </c>
-      <c r="H101">
-        <v>35.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1.091666666666667</v>
-      </c>
-      <c r="K101">
-        <v>0.01300000000000001</v>
-      </c>
-      <c r="L101">
-        <v>1.078666666666667</v>
-      </c>
-      <c r="M101">
-        <v>11.2752486</v>
-      </c>
-      <c r="N101">
-        <v>-10.19658193333334</v>
-      </c>
-      <c r="O101">
-        <v>-0</v>
-      </c>
-      <c r="P101">
-        <v>-10.19658193333334</v>
-      </c>
-      <c r="Q101">
-        <v>-10.18358193333334</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.902474897695588</v>
-      </c>
-      <c r="T101">
-        <v>75.17377218129916</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0</v>
-      </c>
-      <c r="W101">
-        <v>0.2358</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.09566677462585316</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
